--- a/outputs/daily/hr_rankings_2026-08-25_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-25_remaining.xlsx
@@ -10090,34 +10090,30 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -17070,34 +17066,30 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB60" t="inlineStr"/>
       <c r="AC60" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22402,34 +22394,30 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -27166,34 +27154,30 @@
       </c>
       <c r="W96" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -49214,34 +49198,30 @@
       </c>
       <c r="W175" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB175" t="inlineStr"/>
       <c r="AC175" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -57870,7 +57850,7 @@
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X206" t="inlineStr">
@@ -57895,7 +57875,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 9</t>
+          <t>order MLB 6 vs RotoWire 9</t>
         </is>
       </c>
       <c r="AC206" t="inlineStr">
@@ -62918,7 +62898,7 @@
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X224" t="inlineStr">
@@ -62943,7 +62923,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 6</t>
+          <t>order MLB 7 vs RotoWire 6</t>
         </is>
       </c>
       <c r="AC224" t="inlineStr">
@@ -63202,34 +63182,30 @@
       </c>
       <c r="W225" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X225" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y225" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z225" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X225" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y225" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z225" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB225" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB225" t="inlineStr"/>
       <c r="AC225" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/daily/hr_rankings_2026-08-25_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-25_remaining.xlsx
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>67.2</v>
+        <v>67</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>50.2</v>
       </c>
       <c r="R4" t="n">
-        <v>42.1</v>
+        <v>40.6</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -5824,7 +5824,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>57.6</v>
+        <v>57.4</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>38.5</v>
       </c>
       <c r="R20" t="n">
-        <v>42.1</v>
+        <v>40.6</v>
       </c>
       <c r="S20" t="n">
         <v>100</v>
@@ -6039,7 +6039,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -6104,7 +6104,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>57.6</v>
+        <v>57.3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>50.2</v>
       </c>
       <c r="R21" t="n">
-        <v>42.1</v>
+        <v>40.6</v>
       </c>
       <c r="S21" t="n">
         <v>96.59999999999999</v>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -8015,47 +8015,47 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>695657</t>
+          <t>668227</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Randy Arozarena</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:40:00Z</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -8078,26 +8078,26 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>52</v>
+        <v>39.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>50.2</v>
+        <v>49.1</v>
       </c>
       <c r="R28" t="n">
-        <v>42.1</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T28" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U28" t="n">
-        <v>29.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
@@ -8159,17 +8159,17 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.4% barrel, 27.1 HR allowed</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -8179,112 +8179,112 @@
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>13.03</t>
+          <t>8.84</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>42.61</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>89.05</t>
+          <t>90.95</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>101.8037</t>
+          <t>101.0657</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>0.4366</t>
+          <t>0.4198</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>0.2227</t>
+          <t>0.1683</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>0.3431</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>76.65</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>69.67</t>
+          <t>24.59</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>49.23</t>
+          <t>33.77</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>24.31</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.2375</t>
+          <t>0.1901</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>42.39</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>0.3945</t>
+          <t>0.4191</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
-          <t>0.1644</t>
+          <t>0.1738</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr"/>
@@ -8295,47 +8295,47 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>668227</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Randy Arozarena</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-26T01:40:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>56.3</v>
+        <v>56</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8358,26 +8358,26 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>39.7</v>
+        <v>52</v>
       </c>
       <c r="Q29" t="n">
-        <v>49.1</v>
+        <v>50.2</v>
       </c>
       <c r="R29" t="n">
-        <v>68.40000000000001</v>
+        <v>40.6</v>
       </c>
       <c r="S29" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T29" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U29" t="n">
-        <v>71.59999999999999</v>
+        <v>29.2</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
@@ -8439,17 +8439,17 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.4% barrel, 27.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -8459,112 +8459,112 @@
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>8.84</t>
+          <t>13.03</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>42.61</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>90.95</t>
+          <t>89.05</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>101.0657</t>
+          <t>101.8037</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>0.4198</t>
+          <t>0.4366</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>0.1683</t>
+          <t>0.2227</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>0.3431</t>
+          <t>0.313</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>76.65</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>69.67</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>33.77</t>
+          <t>49.23</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.1901</t>
+          <t>0.2375</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>42.39</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>0.4191</t>
+          <t>0.3945</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>0.1738</t>
+          <t>0.1644</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr"/>
@@ -13660,7 +13660,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>52.3</v>
+        <v>52.1</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>38.5</v>
       </c>
       <c r="R48" t="n">
-        <v>42.1</v>
+        <v>40.6</v>
       </c>
       <c r="S48" t="n">
         <v>76.2</v>
@@ -13875,7 +13875,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI48" t="inlineStr">
@@ -15011,56 +15011,56 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>694671</t>
+          <t>687093</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Wyatt Langford</t>
+          <t>Vaughn Grissom</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:38:00Z</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -15074,26 +15074,26 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>39.8</v>
+        <v>24.8</v>
       </c>
       <c r="Q53" t="n">
-        <v>38.5</v>
+        <v>56.2</v>
       </c>
       <c r="R53" t="n">
-        <v>42.1</v>
+        <v>71.2</v>
       </c>
       <c r="S53" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T53" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U53" t="n">
-        <v>37.8</v>
+        <v>16.6</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -15128,7 +15128,7 @@
       <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr"/>
@@ -15145,27 +15145,27 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 1 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.9% barrel, 24.4 HR allowed</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
@@ -15175,112 +15175,112 @@
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>42.31</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>100.9419</t>
+          <t>99.0516</t>
         </is>
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>0.4137</t>
+          <t>0.377</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>0.1736</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr">
         <is>
-          <t>0.3222</t>
+          <t>0.309</t>
         </is>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>72.68</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>0.2033</t>
+          <t>0.126</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>10.89</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>46.68</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BD53" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>0.4071</t>
         </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1789</t>
         </is>
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BG53" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr"/>
@@ -15291,56 +15291,56 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>687093</t>
+          <t>694671</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Vaughn Grissom</t>
+          <t>Wyatt Langford</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-26T01:38:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -15354,26 +15354,26 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>24.8</v>
+        <v>39.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>56.2</v>
+        <v>38.5</v>
       </c>
       <c r="R54" t="n">
-        <v>71.2</v>
+        <v>40.6</v>
       </c>
       <c r="S54" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T54" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U54" t="n">
-        <v>16.6</v>
+        <v>37.8</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -15408,7 +15408,7 @@
       <c r="AB54" t="inlineStr"/>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr"/>
@@ -15425,27 +15425,27 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.9% barrel, 24.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
@@ -15455,112 +15455,112 @@
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>42.31</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>99.0516</t>
+          <t>100.9419</t>
         </is>
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>0.4137</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.1736</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>0.3222</t>
         </is>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.68</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>28.64</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>0.2033</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>10.89</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>46.68</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD54" t="inlineStr">
         <is>
-          <t>0.4071</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
-          <t>0.1789</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BG54" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ54" t="inlineStr"/>
@@ -16127,52 +16127,52 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>679822</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Justin Foscue</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:40:00Z</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>694973</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L57" t="n">
@@ -16190,26 +16190,26 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>38.6</v>
+        <v>43.5</v>
       </c>
       <c r="Q57" t="n">
-        <v>38.5</v>
+        <v>30.1</v>
       </c>
       <c r="R57" t="n">
-        <v>42.1</v>
+        <v>59.6</v>
       </c>
       <c r="S57" t="n">
-        <v>93.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T57" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U57" t="n">
-        <v>37.8</v>
+        <v>39.5</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -16244,7 +16244,7 @@
       <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr"/>
@@ -16261,12 +16261,12 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -16276,127 +16276,127 @@
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 1 HR</t>
+          <t>Last 7 games: 6/23, 1 HR</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>48.92</t>
+          <t>47.56</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>91.32</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>99.4562</t>
+          <t>101.1459</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>0.3839</t>
+          <t>0.4313</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>0.1677</t>
+          <t>0.1779</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.3308</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>71.77</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>10.22</t>
+          <t>19.39</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>47.97</t>
+          <t>36.57</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>35.23</t>
+          <t>25.53</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>14.7</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>0.1856</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1253</t>
         </is>
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.99</t>
         </is>
       </c>
       <c r="BG57" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI57" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ57" t="inlineStr"/>
@@ -16407,22 +16407,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>669016</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Brandon Marsh</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -16437,17 +16437,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>George Kirby</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>694973</t>
+          <t>669923</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -16456,7 +16456,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -16470,26 +16470,26 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>43.5</v>
+        <v>38</v>
       </c>
       <c r="Q58" t="n">
-        <v>30.1</v>
+        <v>41.5</v>
       </c>
       <c r="R58" t="n">
-        <v>59.6</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="S58" t="n">
-        <v>94.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T58" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U58" t="n">
-        <v>39.5</v>
+        <v>22.9</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -16546,22 +16546,22 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Last 7 games: 6/22, 0 HR</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.4% barrel, 16.4 HR allowed</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
@@ -16571,112 +16571,112 @@
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>8.54</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>47.56</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>91.32</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>101.1459</t>
+          <t>100.2023</t>
         </is>
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>0.4313</t>
+          <t>0.4208</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.1606</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr">
         <is>
-          <t>0.3308</t>
+          <t>0.316</t>
         </is>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>71.77</t>
+          <t>71.54</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>19.39</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>36.57</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>25.53</t>
+          <t>26.45</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>0.1856</t>
+          <t>0.1609</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="BD58" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>0.4025</t>
         </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
-          <t>0.1253</t>
+          <t>0.1451</t>
         </is>
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>23.99</t>
+          <t>24.73</t>
         </is>
       </c>
       <c r="BG58" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI58" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ58" t="inlineStr"/>
@@ -16687,56 +16687,56 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>669016</t>
+          <t>679822</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brandon Marsh</t>
+          <t>Justin Foscue</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-26T01:40:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>George Kirby</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>669923</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -16750,26 +16750,26 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>38</v>
+        <v>38.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>41.5</v>
+        <v>38.5</v>
       </c>
       <c r="R59" t="n">
-        <v>68.40000000000001</v>
+        <v>40.6</v>
       </c>
       <c r="S59" t="n">
-        <v>64.3</v>
+        <v>93.2</v>
       </c>
       <c r="T59" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U59" t="n">
-        <v>22.9</v>
+        <v>37.8</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -16804,7 +16804,7 @@
       <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr"/>
@@ -16821,142 +16821,142 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 0 HR</t>
+          <t>Last 7 games: 5/20, 1 HR</t>
         </is>
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.4% barrel, 16.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>48.92</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>100.2023</t>
+          <t>99.4562</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>0.4208</t>
+          <t>0.3839</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>0.1606</t>
+          <t>0.1677</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.282</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>71.54</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>10.22</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>47.97</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>26.45</t>
+          <t>35.23</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>0.1609</t>
+          <t>0.181</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD59" t="inlineStr">
         <is>
-          <t>0.4025</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
-          <t>0.1451</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF59" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BG59" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI59" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ59" t="inlineStr"/>
@@ -17807,56 +17807,56 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>607043</t>
+          <t>694376</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Shay Whitcomb</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:45:00Z</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Brady Singer</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>663903</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -17870,26 +17870,26 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>48.3</v>
+        <v>41.3</v>
       </c>
       <c r="Q63" t="n">
-        <v>38.5</v>
+        <v>51.7</v>
       </c>
       <c r="R63" t="n">
-        <v>42.1</v>
+        <v>55.8</v>
       </c>
       <c r="S63" t="n">
-        <v>94.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T63" t="n">
         <v>50</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>25.3</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -17924,7 +17924,7 @@
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD63" t="inlineStr"/>
@@ -17946,137 +17946,137 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/27, 0 HR</t>
+          <t>Last 7 games: 2/12, 1 HR</t>
         </is>
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.5% barrel, 23.2 HR allowed</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>11.36</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>35.49</t>
         </is>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>92.11</t>
+          <t>87.93</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
         <is>
-          <t>102.1199</t>
+          <t>97.9997</t>
         </is>
       </c>
       <c r="AR63" t="inlineStr">
         <is>
-          <t>0.4575</t>
+          <t>0.3678</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>0.1852</t>
+          <t>0.2038</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr">
         <is>
-          <t>0.3462</t>
+          <t>0.2337</t>
         </is>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>72.27</t>
+          <t>71.87</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>27.32</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>32.54</t>
+          <t>35.44</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>45.43</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.1614</t>
+          <t>0.1899</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>90.58</t>
         </is>
       </c>
       <c r="BD63" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>0.4356</t>
         </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF63" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="BG63" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BI63" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ63" t="inlineStr"/>
@@ -18087,56 +18087,56 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>694376</t>
+          <t>607043</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Shay Whitcomb</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-26T01:45:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Brady Singer</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>663903</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -18150,26 +18150,26 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>41.3</v>
+        <v>48.3</v>
       </c>
       <c r="Q64" t="n">
-        <v>51.7</v>
+        <v>38.5</v>
       </c>
       <c r="R64" t="n">
-        <v>55.8</v>
+        <v>40.6</v>
       </c>
       <c r="S64" t="n">
-        <v>64.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T64" t="n">
         <v>50</v>
       </c>
       <c r="U64" t="n">
-        <v>25.3</v>
+        <v>0</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -18204,7 +18204,7 @@
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD64" t="inlineStr"/>
@@ -18226,137 +18226,137 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/12, 1 HR</t>
+          <t>Last 7 games: 2/27, 0 HR</t>
         </is>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.5% barrel, 23.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>11.36</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>35.49</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>87.93</t>
+          <t>92.11</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
         <is>
-          <t>97.9997</t>
+          <t>102.1199</t>
         </is>
       </c>
       <c r="AR64" t="inlineStr">
         <is>
-          <t>0.3678</t>
+          <t>0.4575</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>0.2038</t>
+          <t>0.1852</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr">
         <is>
-          <t>0.2337</t>
+          <t>0.3462</t>
         </is>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>71.87</t>
+          <t>72.27</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>27.32</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>35.44</t>
+          <t>32.54</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>45.43</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>16.6</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.1899</t>
+          <t>0.1614</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>90.58</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD64" t="inlineStr">
         <is>
-          <t>0.4356</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF64" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BG64" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI64" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ64" t="inlineStr"/>
@@ -21727,27 +21727,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>687637</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-25T23:45:00Z</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -21757,26 +21757,26 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Matthew Liberatore</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>669461</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>46.9</v>
+        <v>46.8</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -21790,26 +21790,26 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>22.9</v>
+        <v>33.5</v>
       </c>
       <c r="Q77" t="n">
-        <v>48.1</v>
+        <v>53.4</v>
       </c>
       <c r="R77" t="n">
-        <v>42.1</v>
+        <v>47.1</v>
       </c>
       <c r="S77" t="n">
-        <v>94.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T77" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U77" t="n">
-        <v>28.9</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -21844,7 +21844,7 @@
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr"/>
@@ -21866,22 +21866,22 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.5% barrel, 20.4 HR allowed</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
@@ -21891,32 +21891,32 @@
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>8.18</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>36.68</t>
         </is>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>88.87</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
         <is>
-          <t>100.1991</t>
+          <t>99.4568</t>
         </is>
       </c>
       <c r="AR77" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>0.3877</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>0.1635</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr">
@@ -21926,77 +21926,77 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>21.05</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>41.58</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>32.16</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>0.1506</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>41.52</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="BD77" t="inlineStr">
         <is>
-          <t>0.3945</t>
+          <t>0.4482</t>
         </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
-          <t>0.1644</t>
+          <t>0.1815</t>
         </is>
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>29.01</t>
         </is>
       </c>
       <c r="BG77" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BI77" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ77" t="inlineStr"/>
@@ -22007,52 +22007,52 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>687637</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dylan Beavers</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-25T23:45:00Z</t>
+          <t>2026-08-26T01:38:00Z</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Matthew Liberatore</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>669461</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L78" t="n">
@@ -22070,26 +22070,26 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Hot Hitter/Streak</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P78" t="n">
-        <v>33.5</v>
+        <v>37</v>
       </c>
       <c r="Q78" t="n">
-        <v>53.4</v>
+        <v>16.7</v>
       </c>
       <c r="R78" t="n">
-        <v>47.1</v>
+        <v>71.2</v>
       </c>
       <c r="S78" t="n">
-        <v>52.4</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T78" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U78" t="n">
-        <v>79.90000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
@@ -22124,7 +22124,7 @@
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr"/>
@@ -22141,27 +22141,27 @@
       </c>
       <c r="AH78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.5% barrel, 20.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.3% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
@@ -22171,112 +22171,112 @@
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>36.68</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>88.87</t>
+          <t>89.14</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>99.4568</t>
+          <t>100.9008</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>0.3877</t>
+          <t>0.4213</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>0.1635</t>
+          <t>0.166</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.3275</t>
         </is>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>21.05</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>41.58</t>
+          <t>35.17</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>32.16</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>15.2</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>0.1506</t>
+          <t>0.1908</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>41.52</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="BD78" t="inlineStr">
         <is>
-          <t>0.4482</t>
+          <t>0.301</t>
         </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
-          <t>0.1815</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>29.01</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="BG78" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI78" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ78" t="inlineStr"/>
@@ -22287,47 +22287,47 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-26T01:38:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -22336,7 +22336,7 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -22350,26 +22350,26 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>37</v>
+        <v>22.9</v>
       </c>
       <c r="Q79" t="n">
-        <v>16.7</v>
+        <v>48.1</v>
       </c>
       <c r="R79" t="n">
-        <v>71.2</v>
+        <v>40.6</v>
       </c>
       <c r="S79" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T79" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U79" t="n">
-        <v>10.8</v>
+        <v>28.9</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -22404,7 +22404,7 @@
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr"/>
@@ -22421,27 +22421,27 @@
       </c>
       <c r="AH79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.3% barrel, 7.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
@@ -22451,112 +22451,112 @@
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>89.14</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>100.9008</t>
+          <t>100.1991</t>
         </is>
       </c>
       <c r="AR79" t="inlineStr">
         <is>
-          <t>0.4213</t>
+          <t>0.371</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>0.131</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr">
         <is>
-          <t>0.3275</t>
+          <t>0.316</t>
         </is>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>35.17</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>0.1908</t>
+          <t>0.141</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD79" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>0.3945</t>
         </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.1644</t>
         </is>
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="BG79" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI79" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ79" t="inlineStr"/>
@@ -25363,47 +25363,47 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>672515</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Gabriel Moreno</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:40:00Z</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Clay Holmes</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>605280</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -25426,50 +25426,42 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>19.6</v>
+        <v>37</v>
       </c>
       <c r="Q90" t="n">
-        <v>50.2</v>
+        <v>29.2</v>
       </c>
       <c r="R90" t="n">
-        <v>42.1</v>
+        <v>41.7</v>
       </c>
       <c r="S90" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T90" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U90" t="n">
-        <v>2.5</v>
+        <v>34.9</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -25477,10 +25469,14 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD90" t="inlineStr"/>
@@ -25497,27 +25493,27 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 0 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.5% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
@@ -25527,112 +25523,112 @@
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.73</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>33.5</t>
+          <t>42.91</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>97.7459</t>
+          <t>99.7102</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.4558</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.1677</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.3614</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>71.39</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>19.93</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>25.89</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0.1557</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>5.47</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>42.02</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>89.56</t>
         </is>
       </c>
       <c r="BD90" t="inlineStr">
         <is>
-          <t>0.3945</t>
+          <t>0.3786</t>
         </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
-          <t>0.1644</t>
+          <t>0.1241</t>
         </is>
       </c>
       <c r="BF90" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BG90" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI90" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ90" t="inlineStr"/>
@@ -25643,47 +25639,47 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>672515</t>
+          <t>803011</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Gabriel Moreno</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-26T01:40:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Clay Holmes</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>605280</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -25692,7 +25688,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>45.2</v>
+        <v>45</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -25706,57 +25702,61 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>37</v>
+        <v>19.6</v>
       </c>
       <c r="Q91" t="n">
-        <v>29.2</v>
+        <v>50.2</v>
       </c>
       <c r="R91" t="n">
-        <v>41.7</v>
+        <v>40.6</v>
       </c>
       <c r="S91" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T91" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U91" t="n">
-        <v>34.9</v>
+        <v>2.5</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W91" t="inlineStr"/>
-      <c r="X91" t="inlineStr"/>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="Y91" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB91" t="inlineStr"/>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD91" t="inlineStr"/>
@@ -25773,27 +25773,27 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Last 7 games: 3/22, 0 HR</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.5% barrel, 7.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
@@ -25803,112 +25803,112 @@
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>42.91</t>
+          <t>33.5</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>99.7102</t>
+          <t>97.7459</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
         <is>
-          <t>0.4558</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>0.1677</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>0.3614</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>71.39</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>19.93</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>33.8</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>25.89</t>
+          <t>21.7</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>0.1557</t>
+          <t>0.121</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>5.47</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>42.02</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>89.56</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD91" t="inlineStr">
         <is>
-          <t>0.3786</t>
+          <t>0.3945</t>
         </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
-          <t>0.1241</t>
+          <t>0.1644</t>
         </is>
       </c>
       <c r="BF91" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="BG91" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI91" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ91" t="inlineStr"/>
@@ -26528,7 +26528,7 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>44.5</v>
+        <v>44.3</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>38.5</v>
       </c>
       <c r="R94" t="n">
-        <v>42.1</v>
+        <v>40.6</v>
       </c>
       <c r="S94" t="n">
         <v>86.40000000000001</v>
@@ -26743,7 +26743,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI94" t="inlineStr">
@@ -26759,56 +26759,56 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>681351</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Logan O'Hoppe</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:38:00Z</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -26822,26 +26822,26 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>34.9</v>
+        <v>20.9</v>
       </c>
       <c r="Q95" t="n">
-        <v>38.5</v>
+        <v>16.7</v>
       </c>
       <c r="R95" t="n">
-        <v>42.1</v>
+        <v>71.2</v>
       </c>
       <c r="S95" t="n">
-        <v>64.3</v>
+        <v>100</v>
       </c>
       <c r="T95" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U95" t="n">
-        <v>17.7</v>
+        <v>22.4</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
@@ -26876,7 +26876,7 @@
       <c r="AB95" t="inlineStr"/>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD95" t="inlineStr"/>
@@ -26893,12 +26893,12 @@
       </c>
       <c r="AH95" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -26908,12 +26908,12 @@
       </c>
       <c r="AK95" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.3% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AM95" t="inlineStr">
@@ -26923,112 +26923,112 @@
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>88.17</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="AQ95" t="inlineStr">
         <is>
-          <t>99.6818</t>
+          <t>98.5252</t>
         </is>
       </c>
       <c r="AR95" t="inlineStr">
         <is>
-          <t>0.3585</t>
+          <t>0.351</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr">
         <is>
-          <t>0.1508</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr">
         <is>
-          <t>0.2758</t>
+          <t>0.302</t>
         </is>
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>72.04</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>0.1062</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>5.3</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>34.3</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="BD95" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>0.301</t>
         </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="BF95" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.1</t>
         </is>
       </c>
       <c r="BG95" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>90</t>
         </is>
       </c>
       <c r="BI95" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ95" t="inlineStr"/>
@@ -27039,27 +27039,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-26T01:38:00Z</t>
+          <t>2026-08-26T01:40:00Z</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -27069,22 +27069,22 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Gage Jump</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>695611</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -27102,26 +27102,26 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Good Environment, Premium Lineup Spot, Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>20.9</v>
+        <v>19.7</v>
       </c>
       <c r="Q96" t="n">
-        <v>16.7</v>
+        <v>31.1</v>
       </c>
       <c r="R96" t="n">
-        <v>71.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="S96" t="n">
-        <v>100</v>
+        <v>64.3</v>
       </c>
       <c r="T96" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U96" t="n">
-        <v>22.4</v>
+        <v>60.7</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -27135,7 +27135,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
@@ -27156,7 +27156,7 @@
       <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD96" t="inlineStr"/>
@@ -27178,22 +27178,22 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.3% barrel, 7.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.1% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
@@ -27203,97 +27203,97 @@
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>34.58</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>88.11</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>98.5252</t>
+          <t>97.5322</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>0.3467</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>0.2771</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>18.8</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.169</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BD96" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BF96" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="BG96" t="inlineStr">
@@ -27303,12 +27303,12 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>93</t>
         </is>
       </c>
       <c r="BI96" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ96" t="inlineStr"/>
@@ -27319,22 +27319,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>641487</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>J.P. Crawford</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -27349,22 +27349,22 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Gage Jump</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>695611</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L97" t="n">
@@ -27382,26 +27382,26 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>19.7</v>
+        <v>21.4</v>
       </c>
       <c r="Q97" t="n">
-        <v>31.1</v>
+        <v>49.1</v>
       </c>
       <c r="R97" t="n">
-        <v>74.40000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="S97" t="n">
-        <v>64.3</v>
+        <v>52.4</v>
       </c>
       <c r="T97" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U97" t="n">
-        <v>60.7</v>
+        <v>4.5</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -27415,7 +27415,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -27436,7 +27436,7 @@
       <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr"/>
@@ -27453,27 +27453,27 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/20, 0 HR</t>
         </is>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.1% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.4% barrel, 27.1 HR allowed</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
@@ -27483,97 +27483,97 @@
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>5.95</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>34.58</t>
+          <t>35.12</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>88.11</t>
+          <t>87.48</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>97.5322</t>
+          <t>98.2679</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>0.3467</t>
+          <t>0.3713</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1235</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>0.2771</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>71.28</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>18.88</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>10.6</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>0.1246</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>42.39</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="BD97" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.4191</t>
         </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.1738</t>
         </is>
       </c>
       <c r="BF97" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="BG97" t="inlineStr">
@@ -27583,12 +27583,12 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BI97" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ97" t="inlineStr"/>
@@ -27599,27 +27599,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>641487</t>
+          <t>687529</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>J.P. Crawford</t>
+          <t>Grant McCray</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-26T01:40:00Z</t>
+          <t>2026-08-26T01:45:00Z</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -27634,12 +27634,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Brady Singer</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>663903</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -27662,17 +27662,17 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>21.4</v>
+        <v>26</v>
       </c>
       <c r="Q98" t="n">
-        <v>49.1</v>
+        <v>51.7</v>
       </c>
       <c r="R98" t="n">
-        <v>68.40000000000001</v>
+        <v>55.8</v>
       </c>
       <c r="S98" t="n">
         <v>52.4</v>
@@ -27681,7 +27681,7 @@
         <v>80</v>
       </c>
       <c r="U98" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -27733,12 +27733,12 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
@@ -27748,12 +27748,12 @@
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 1/15, 0 HR</t>
         </is>
       </c>
       <c r="AL98" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.4% barrel, 27.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.5% barrel, 23.2 HR allowed</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
@@ -27763,97 +27763,97 @@
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>5.95</t>
+          <t>11.83</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>35.12</t>
+          <t>26.25</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>87.48</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>98.2679</t>
+          <t>98.3932</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
         <is>
-          <t>0.3713</t>
+          <t>0.3126</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>0.1235</t>
+          <t>0.1344</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.2683</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>71.28</t>
+          <t>72.43</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>18.88</t>
+          <t>26.11</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>40.29</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>0.1246</t>
+          <t>0.1148</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>42.39</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>90.58</t>
         </is>
       </c>
       <c r="BD98" t="inlineStr">
         <is>
-          <t>0.4191</t>
+          <t>0.4356</t>
         </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
-          <t>0.1738</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF98" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="BG98" t="inlineStr">
@@ -27863,12 +27863,12 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BI98" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ98" t="inlineStr"/>
@@ -27879,56 +27879,56 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>687529</t>
+          <t>681351</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Grant McCray</t>
+          <t>Logan O'Hoppe</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-26T01:45:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Brady Singer</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>663903</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L99" t="n">
-        <v>43.9</v>
+        <v>43.8</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -27946,22 +27946,22 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>26</v>
+        <v>34.9</v>
       </c>
       <c r="Q99" t="n">
-        <v>51.7</v>
+        <v>38.5</v>
       </c>
       <c r="R99" t="n">
-        <v>55.8</v>
+        <v>40.6</v>
       </c>
       <c r="S99" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T99" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>17.7</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
@@ -27996,7 +27996,7 @@
       <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr"/>
@@ -28013,12 +28013,12 @@
       </c>
       <c r="AH99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
@@ -28028,12 +28028,12 @@
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/15, 0 HR</t>
+          <t>Last 7 games: 5/21, 0 HR</t>
         </is>
       </c>
       <c r="AL99" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.5% barrel, 23.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
@@ -28043,112 +28043,112 @@
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>11.83</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>26.25</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>88.17</t>
         </is>
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>98.3932</t>
+          <t>99.6818</t>
         </is>
       </c>
       <c r="AR99" t="inlineStr">
         <is>
-          <t>0.3126</t>
+          <t>0.3585</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>0.1344</t>
+          <t>0.1508</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr">
         <is>
-          <t>0.2683</t>
+          <t>0.2758</t>
         </is>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>72.43</t>
+          <t>72.04</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>26.11</t>
+          <t>23.98</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>40.29</t>
+          <t>44.24</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>0.1148</t>
+          <t>0.1062</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>90.58</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD99" t="inlineStr">
         <is>
-          <t>0.4356</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF99" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BG99" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI99" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ99" t="inlineStr"/>
@@ -29275,47 +29275,47 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>671976</t>
+          <t>701852</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tristan Peters</t>
+          <t>Drew Cavanaugh</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:45:00Z</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Brady Singer</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>663903</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -29338,26 +29338,26 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>13.4</v>
+        <v>7</v>
       </c>
       <c r="Q104" t="n">
-        <v>50.2</v>
+        <v>51.7</v>
       </c>
       <c r="R104" t="n">
-        <v>42.1</v>
+        <v>55.8</v>
       </c>
       <c r="S104" t="n">
-        <v>64.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T104" t="n">
         <v>80</v>
       </c>
       <c r="U104" t="n">
-        <v>76.09999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -29371,7 +29371,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
@@ -29392,7 +29392,7 @@
       <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr"/>
@@ -29409,27 +29409,27 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.5% barrel, 23.2 HR allowed</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
@@ -29439,112 +29439,112 @@
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>97.9501</t>
+          <t>97.8732</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>0.3222</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>0.1015</t>
+          <t>0.098</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>69.16</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>42.33</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>18.41</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>0.1211</t>
+          <t>0.012</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>9.47</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>90.58</t>
         </is>
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>0.3945</t>
+          <t>0.4356</t>
         </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
-          <t>0.1644</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="BG104" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BI104" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ104" t="inlineStr"/>
@@ -29555,47 +29555,47 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>701852</t>
+          <t>671976</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Drew Cavanaugh</t>
+          <t>Tristan Peters</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-26T01:45:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Brady Singer</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>663903</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -29604,7 +29604,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -29618,26 +29618,26 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>7</v>
+        <v>13.4</v>
       </c>
       <c r="Q105" t="n">
-        <v>51.7</v>
+        <v>50.2</v>
       </c>
       <c r="R105" t="n">
-        <v>55.8</v>
+        <v>40.6</v>
       </c>
       <c r="S105" t="n">
-        <v>86.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T105" t="n">
         <v>80</v>
       </c>
       <c r="U105" t="n">
-        <v>9.300000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
@@ -29672,7 +29672,7 @@
       <c r="AB105" t="inlineStr"/>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr"/>
@@ -29689,27 +29689,27 @@
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.5% barrel, 23.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
@@ -29719,112 +29719,112 @@
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>97.8732</t>
+          <t>97.9501</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3222</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>0.1015</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>69.16</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>42.33</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0.1211</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>90.58</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD105" t="inlineStr">
         <is>
-          <t>0.4356</t>
+          <t>0.3945</t>
         </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.1644</t>
         </is>
       </c>
       <c r="BF105" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="BG105" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI105" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ105" t="inlineStr"/>
@@ -34863,47 +34863,47 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>686668</t>
+          <t>663968</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brenton Doyle</t>
+          <t>Jake Mangum</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:40:00Z</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>650633</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -34926,26 +34926,26 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P124" t="n">
-        <v>24</v>
+        <v>6.3</v>
       </c>
       <c r="Q124" t="n">
-        <v>50.2</v>
+        <v>39.3</v>
       </c>
       <c r="R124" t="n">
-        <v>42.1</v>
+        <v>59.6</v>
       </c>
       <c r="S124" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T124" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U124" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V124" t="inlineStr">
         <is>
@@ -34959,7 +34959,7 @@
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -34997,27 +34997,27 @@
       </c>
       <c r="AH124" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK124" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/10, 0 HR</t>
+          <t>Last 7 games: 3/20, 0 HR</t>
         </is>
       </c>
       <c r="AL124" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.4% barrel, 16.2 HR allowed</t>
         </is>
       </c>
       <c r="AM124" t="inlineStr">
@@ -35027,112 +35027,112 @@
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>36.27</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AQ124" t="inlineStr">
         <is>
-          <t>99.2931</t>
+          <t>96.7083</t>
         </is>
       </c>
       <c r="AR124" t="inlineStr">
         <is>
-          <t>0.3184</t>
+          <t>0.3325</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>0.1098</t>
+          <t>0.0822</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>0.283</t>
         </is>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>71.68</t>
+          <t>67.58</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>12.57</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>25.27</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>0.0975</t>
+          <t>0.0846</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>34.11</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="BD124" t="inlineStr">
         <is>
-          <t>0.3945</t>
+          <t>0.4095</t>
         </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
-          <t>0.1644</t>
+          <t>0.173</t>
         </is>
       </c>
       <c r="BF124" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BG124" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH124" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI124" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ124" t="inlineStr"/>
@@ -35143,47 +35143,47 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>663968</t>
+          <t>686668</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-26T01:40:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Michael King</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>650633</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -35192,7 +35192,7 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>38.1</v>
+        <v>37.9</v>
       </c>
       <c r="M125" t="inlineStr">
         <is>
@@ -35206,26 +35206,26 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>6.3</v>
+        <v>24</v>
       </c>
       <c r="Q125" t="n">
-        <v>39.3</v>
+        <v>50.2</v>
       </c>
       <c r="R125" t="n">
-        <v>59.6</v>
+        <v>40.6</v>
       </c>
       <c r="S125" t="n">
-        <v>76.2</v>
+        <v>52.4</v>
       </c>
       <c r="T125" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U125" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V125" t="inlineStr">
         <is>
@@ -35239,7 +35239,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
@@ -35277,12 +35277,12 @@
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AJ125" t="inlineStr">
@@ -35292,12 +35292,12 @@
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 0/10, 0 HR</t>
         </is>
       </c>
       <c r="AL125" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.4% barrel, 16.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
@@ -35307,112 +35307,112 @@
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>36.27</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AQ125" t="inlineStr">
         <is>
-          <t>96.7083</t>
+          <t>99.2931</t>
         </is>
       </c>
       <c r="AR125" t="inlineStr">
         <is>
-          <t>0.3325</t>
+          <t>0.3184</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>0.0822</t>
+          <t>0.1098</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>0.258</t>
         </is>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>67.58</t>
+          <t>71.68</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>12.57</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>25.27</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>0.0846</t>
+          <t>0.0975</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>34.11</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD125" t="inlineStr">
         <is>
-          <t>0.4095</t>
+          <t>0.3945</t>
         </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>0.1644</t>
         </is>
       </c>
       <c r="BF125" t="inlineStr">
         <is>
-          <t>27.82</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="BG125" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH125" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI125" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ125" t="inlineStr"/>
@@ -35472,7 +35472,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>37.9</v>
+        <v>37.7</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>50.2</v>
       </c>
       <c r="R126" t="n">
-        <v>42.1</v>
+        <v>40.6</v>
       </c>
       <c r="S126" t="n">
         <v>76.2</v>
@@ -35687,7 +35687,7 @@
       </c>
       <c r="BH126" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI126" t="inlineStr">
@@ -37103,32 +37103,32 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>691011</t>
+          <t>670770</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Drew Romo</t>
+          <t>TJ Friedl</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:45:00Z</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -37138,12 +37138,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Jacob deGrom</t>
+          <t>Adrian Houser</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>594798</t>
+          <t>605288</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -37152,7 +37152,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
@@ -37170,22 +37170,22 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="Q132" t="n">
-        <v>48.1</v>
+        <v>45.6</v>
       </c>
       <c r="R132" t="n">
-        <v>42.1</v>
+        <v>55.8</v>
       </c>
       <c r="S132" t="n">
         <v>44.8</v>
       </c>
       <c r="T132" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U132" t="n">
-        <v>37.8</v>
+        <v>0</v>
       </c>
       <c r="V132" t="inlineStr">
         <is>
@@ -37237,27 +37237,27 @@
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/16, 1 HR</t>
+          <t>Last 7 games: 1/12, 0 HR</t>
         </is>
       </c>
       <c r="AL132" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.0% barrel, 13.5 HR allowed</t>
         </is>
       </c>
       <c r="AM132" t="inlineStr">
@@ -37267,112 +37267,112 @@
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.88</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>95.305</t>
+          <t>97.0031</t>
         </is>
       </c>
       <c r="AR132" t="inlineStr">
         <is>
-          <t>0.2086</t>
+          <t>0.2631</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>0.0777</t>
+          <t>0.0732</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>0.1785</t>
+          <t>0.2531</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>68.49</t>
+          <t>70.67</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>9.54</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>24.89</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.089</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>8.95</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>43.82</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="BD132" t="inlineStr">
         <is>
-          <t>0.3945</t>
+          <t>0.4353</t>
         </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
-          <t>0.1644</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BF132" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="BG132" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH132" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BI132" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ132" t="inlineStr"/>
@@ -37383,32 +37383,32 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>670770</t>
+          <t>691011</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TJ Friedl</t>
+          <t>Drew Romo</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-08-26T01:45:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -37418,12 +37418,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Adrian Houser</t>
+          <t>Jacob deGrom</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>605288</t>
+          <t>594798</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -37432,7 +37432,7 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
@@ -37450,22 +37450,22 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>9.4</v>
+        <v>9.9</v>
       </c>
       <c r="Q133" t="n">
-        <v>45.6</v>
+        <v>48.1</v>
       </c>
       <c r="R133" t="n">
-        <v>55.8</v>
+        <v>40.6</v>
       </c>
       <c r="S133" t="n">
         <v>44.8</v>
       </c>
       <c r="T133" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U133" t="n">
-        <v>0</v>
+        <v>37.8</v>
       </c>
       <c r="V133" t="inlineStr">
         <is>
@@ -37517,27 +37517,27 @@
       </c>
       <c r="AH133" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/12, 0 HR</t>
+          <t>Last 7 games: 4/16, 1 HR</t>
         </is>
       </c>
       <c r="AL133" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.0% barrel, 13.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.9% barrel, 19.7 HR allowed</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
@@ -37547,112 +37547,112 @@
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>28.88</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
-          <t>97.0031</t>
+          <t>95.305</t>
         </is>
       </c>
       <c r="AR133" t="inlineStr">
         <is>
-          <t>0.2631</t>
+          <t>0.2086</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>0.0732</t>
+          <t>0.0777</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr">
         <is>
-          <t>0.2531</t>
+          <t>0.1785</t>
         </is>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>68.49</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>9.54</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>24.89</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>8.95</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="BD133" t="inlineStr">
         <is>
-          <t>0.4353</t>
+          <t>0.3945</t>
         </is>
       </c>
       <c r="BE133" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.1644</t>
         </is>
       </c>
       <c r="BF133" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>29.74</t>
         </is>
       </c>
       <c r="BG133" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH133" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI133" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ133" t="inlineStr"/>
@@ -38223,56 +38223,56 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>643376</t>
+          <t>663538</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Danny Jansen</t>
+          <t>Nico Hoerner</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:40:00Z</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Brandon Pfaadt</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>694297</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
@@ -38286,26 +38286,26 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P136" t="n">
-        <v>19.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q136" t="n">
-        <v>38.5</v>
+        <v>40.8</v>
       </c>
       <c r="R136" t="n">
-        <v>42.1</v>
+        <v>41.7</v>
       </c>
       <c r="S136" t="n">
-        <v>44.8</v>
+        <v>76.2</v>
       </c>
       <c r="T136" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U136" t="n">
-        <v>0</v>
+        <v>26.4</v>
       </c>
       <c r="V136" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y136" t="inlineStr">
@@ -38340,7 +38340,7 @@
       <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr"/>
@@ -38357,12 +38357,12 @@
       </c>
       <c r="AH136" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
@@ -38372,12 +38372,12 @@
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/15, 0 HR</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL136" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM136" t="inlineStr">
@@ -38387,112 +38387,112 @@
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>28.62</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>87.11</t>
+          <t>86.14</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>97.4711</t>
+          <t>96.2188</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
         <is>
-          <t>0.2888</t>
+          <t>0.3784</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>0.1164</t>
+          <t>0.0815</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>0.2598</t>
+          <t>0.3234</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>70.06</t>
+          <t>68.33</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>54.75</t>
+          <t>32.87</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>28.56</t>
+          <t>21.42</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.31</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>38.24</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.19</t>
         </is>
       </c>
       <c r="BD136" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>0.4107</t>
         </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1603</t>
         </is>
       </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>22.71</t>
         </is>
       </c>
       <c r="BG136" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH136" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI136" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ136" t="inlineStr"/>
@@ -38503,56 +38503,56 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>663538</t>
+          <t>643376</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Nico Hoerner</t>
+          <t>Danny Jansen</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-08-26T01:40:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Brandon Pfaadt</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>694297</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
@@ -38566,26 +38566,26 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P137" t="n">
-        <v>8.199999999999999</v>
+        <v>19.6</v>
       </c>
       <c r="Q137" t="n">
-        <v>40.8</v>
+        <v>38.5</v>
       </c>
       <c r="R137" t="n">
-        <v>41.7</v>
+        <v>40.6</v>
       </c>
       <c r="S137" t="n">
-        <v>76.2</v>
+        <v>44.8</v>
       </c>
       <c r="T137" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U137" t="n">
-        <v>26.4</v>
+        <v>0</v>
       </c>
       <c r="V137" t="inlineStr">
         <is>
@@ -38599,7 +38599,7 @@
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
@@ -38620,7 +38620,7 @@
       <c r="AB137" t="inlineStr"/>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr"/>
@@ -38637,12 +38637,12 @@
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
@@ -38652,12 +38652,12 @@
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/27, 0 HR</t>
+          <t>Last 7 games: 1/15, 0 HR</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 15.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
@@ -38667,112 +38667,112 @@
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>86.14</t>
+          <t>87.11</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>96.2188</t>
+          <t>97.4711</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
         <is>
-          <t>0.3784</t>
+          <t>0.2888</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>0.0815</t>
+          <t>0.1164</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>0.3234</t>
+          <t>0.2598</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>70.06</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>32.87</t>
+          <t>54.75</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>21.42</t>
+          <t>28.56</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>38.24</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD137" t="inlineStr">
         <is>
-          <t>0.4107</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="BE137" t="inlineStr">
         <is>
-          <t>0.1603</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF137" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BG137" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH137" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI137" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ137" t="inlineStr"/>
@@ -39899,56 +39899,56 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>683227</t>
+          <t>687957</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Cody Freeman</t>
+          <t>Dustin Harris</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-25T23:40:00Z</t>
+          <t>2026-08-26T01:40:00Z</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>694973</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
@@ -39966,22 +39966,22 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="Q142" t="n">
-        <v>38.5</v>
+        <v>30.1</v>
       </c>
       <c r="R142" t="n">
-        <v>42.1</v>
+        <v>59.6</v>
       </c>
       <c r="S142" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T142" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U142" t="n">
-        <v>40.3</v>
+        <v>32</v>
       </c>
       <c r="V142" t="inlineStr">
         <is>
@@ -39995,7 +39995,7 @@
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y142" t="inlineStr">
@@ -40016,7 +40016,7 @@
       <c r="AB142" t="inlineStr"/>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD142" t="inlineStr"/>
@@ -40033,12 +40033,12 @@
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
@@ -40048,12 +40048,12 @@
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL142" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
@@ -40063,112 +40063,112 @@
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>23.56</t>
+          <t>17.78</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>84.27</t>
+          <t>84.73</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>94.766</t>
+          <t>93.9291</t>
         </is>
       </c>
       <c r="AR142" t="inlineStr">
         <is>
-          <t>0.2553</t>
+          <t>0.3142</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>0.0499</t>
+          <t>0.0715</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>0.2388</t>
+          <t>0.2884</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>66.74</t>
+          <t>66.75</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>49.46</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>0.0692</t>
+          <t>0.1038</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>39.7</t>
+          <t>39.33</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="BD142" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="BE142" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.1253</t>
         </is>
       </c>
       <c r="BF142" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>23.99</t>
         </is>
       </c>
       <c r="BG142" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH142" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI142" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ142" t="inlineStr"/>
@@ -40179,56 +40179,56 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>687957</t>
+          <t>683227</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Dustin Harris</t>
+          <t>Cody Freeman</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-08-26T01:40:00Z</t>
+          <t>2026-08-25T23:40:00Z</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>694973</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -40246,22 +40246,22 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="Q143" t="n">
-        <v>30.1</v>
+        <v>38.5</v>
       </c>
       <c r="R143" t="n">
-        <v>59.6</v>
+        <v>40.6</v>
       </c>
       <c r="S143" t="n">
-        <v>44.8</v>
+        <v>52.4</v>
       </c>
       <c r="T143" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U143" t="n">
-        <v>32</v>
+        <v>40.3</v>
       </c>
       <c r="V143" t="inlineStr">
         <is>
@@ -40275,7 +40275,7 @@
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
@@ -40296,7 +40296,7 @@
       <c r="AB143" t="inlineStr"/>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr"/>
@@ -40313,12 +40313,12 @@
       </c>
       <c r="AH143" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
@@ -40328,12 +40328,12 @@
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Contact streak: 7/18 over last 7 games</t>
         </is>
       </c>
       <c r="AL143" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM143" t="inlineStr">
@@ -40343,112 +40343,112 @@
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>17.78</t>
+          <t>23.56</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>84.73</t>
+          <t>84.27</t>
         </is>
       </c>
       <c r="AQ143" t="inlineStr">
         <is>
-          <t>93.9291</t>
+          <t>94.766</t>
         </is>
       </c>
       <c r="AR143" t="inlineStr">
         <is>
-          <t>0.3142</t>
+          <t>0.2553</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>0.0715</t>
+          <t>0.0499</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr">
         <is>
-          <t>0.2884</t>
+          <t>0.2388</t>
         </is>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>66.75</t>
+          <t>66.74</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>49.46</t>
+          <t>45.94</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>0.1038</t>
+          <t>0.0692</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>39.33</t>
+          <t>39.7</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD143" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="BE143" t="inlineStr">
         <is>
-          <t>0.1253</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BF143" t="inlineStr">
         <is>
-          <t>23.99</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="BG143" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH143" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI143" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ143" t="inlineStr"/>
@@ -41950,7 +41950,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>67.2</v>
+        <v>67</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -41974,7 +41974,7 @@
         <v>50.2</v>
       </c>
       <c r="R4" t="n">
-        <v>42.1</v>
+        <v>40.6</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -42165,7 +42165,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -46430,7 +46430,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>57.6</v>
+        <v>57.4</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -46454,7 +46454,7 @@
         <v>38.5</v>
       </c>
       <c r="R20" t="n">
-        <v>42.1</v>
+        <v>40.6</v>
       </c>
       <c r="S20" t="n">
         <v>100</v>
@@ -46645,7 +46645,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -46710,7 +46710,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>57.6</v>
+        <v>57.3</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>50.2</v>
       </c>
       <c r="R21" t="n">
-        <v>42.1</v>
+        <v>40.6</v>
       </c>
       <c r="S21" t="n">
         <v>96.59999999999999</v>
@@ -46925,7 +46925,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-08-25_remaining.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-25_remaining.xlsx
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Contact streak: 11/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3735,27 +3735,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>700250</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Ben Rice</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-26T20:07:00Z</t>
+          <t>2026-08-26T23:05:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3798,26 +3798,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>55.6</v>
+        <v>64.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>56.9</v>
+        <v>33</v>
       </c>
       <c r="R13" t="n">
-        <v>28.2</v>
+        <v>38.2</v>
       </c>
       <c r="S13" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>74.2</v>
+        <v>36.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3873,134 +3873,134 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.9% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>50.85</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>90.86</t>
+          <t>92.53</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>103.18</t>
+          <t>102.5716</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4853</t>
+          <t>0.5173</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.2246</t>
+          <t>0.2513</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3426</t>
+          <t>0.3756</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>77.32</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>71.41</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38.28</t>
+          <t>46.29</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1937</t>
+          <t>0.2664</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -4011,27 +4011,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>665833</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oneil Cruz</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-26T20:10:00Z</t>
+          <t>2026-08-26T20:07:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4041,12 +4041,24 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Grayson Rodriguez</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>680570</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
         <v>57.1</v>
       </c>
@@ -4062,26 +4074,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>74.3</v>
+        <v>55.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>56.9</v>
       </c>
       <c r="R14" t="n">
-        <v>22.6</v>
+        <v>28.2</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>48.7</v>
+        <v>74.2</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4095,7 +4107,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4120,7 +4132,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -4137,12 +4149,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -4157,90 +4169,114 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.9% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>57.58</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>95.73</t>
+          <t>90.86</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>107.1754</t>
+          <t>103.18</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4726</t>
+          <t>0.4853</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.2315</t>
+          <t>0.2246</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3471</t>
+          <t>0.3426</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>78.38</t>
+          <t>77.32</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>76.24</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>38.28</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.2088</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+          <t>0.1937</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>46.5</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>90.7</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.477</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>26.2</t>
+        </is>
+      </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -4251,27 +4287,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>700250</t>
+          <t>665833</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ben Rice</t>
+          <t>Oneil Cruz</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-26T23:05:00Z</t>
+          <t>2026-08-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4281,26 +4317,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Peter Lambert</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>663567</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>57</v>
+        <v>57.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4314,26 +4338,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>64.3</v>
+        <v>74.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>33</v>
+        <v>41.2</v>
       </c>
       <c r="R15" t="n">
-        <v>38.2</v>
+        <v>22.6</v>
       </c>
       <c r="S15" t="n">
-        <v>95.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U15" t="n">
-        <v>31.6</v>
+        <v>48.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4347,7 +4371,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4372,7 +4396,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4389,134 +4413,110 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 12.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>57.58</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>92.53</t>
+          <t>95.73</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>102.5716</t>
+          <t>107.1754</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.5173</t>
+          <t>0.4726</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.2513</t>
+          <t>0.2315</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3756</t>
+          <t>0.3471</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>78.38</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>76.24</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>46.29</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.2664</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>6.8</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>36.6</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0.347</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
+          <t>0.2088</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -5128,7 +5128,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>54.7</v>
+        <v>54.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>89.2</v>
+        <v>93.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -5217,12 +5217,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -7215,27 +7215,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>680664</t>
+          <t>687952</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eduardo Valencia</t>
+          <t>Christian Encarnacion-Strand</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-26T17:10:00Z</t>
+          <t>2026-08-26T23:45:00Z</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Michael McGreevy</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>700241</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -7264,7 +7264,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>53.3</v>
+        <v>53.4</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7282,13 +7282,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>70.40000000000001</v>
+        <v>56.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>35.8</v>
+        <v>53.9</v>
       </c>
       <c r="R26" t="n">
-        <v>27.6</v>
+        <v>22.1</v>
       </c>
       <c r="S26" t="n">
         <v>81.90000000000001</v>
@@ -7297,7 +7297,7 @@
         <v>50</v>
       </c>
       <c r="U26" t="n">
-        <v>27.6</v>
+        <v>51.3</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr"/>
@@ -7353,27 +7353,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.2% barrel, 21.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.6% barrel, 16.2 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -7383,59 +7383,59 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>14.67</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.63</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>102.3181</t>
+          <t>101.5339</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.4792</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>0.3133</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.81</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
+          <t>37.81</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>43.08</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
           <t>30.0</t>
         </is>
       </c>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>36.2</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>27.7</t>
-        </is>
-      </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>6.0</t>
@@ -7443,44 +7443,44 @@
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>0.211</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>41.71</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>87.79</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.3799</t>
+          <t>0.4738</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.1487</t>
+          <t>0.1956</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr"/>
       <c r="BH26" t="inlineStr"/>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -7491,27 +7491,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>695734</t>
+          <t>680664</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>Eduardo Valencia</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-26T22:45:00Z</t>
+          <t>2026-08-26T17:10:00Z</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7521,17 +7521,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Tanner Gordon</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>685299</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -7554,26 +7554,26 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>33</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>62.6</v>
+        <v>35.8</v>
       </c>
       <c r="R27" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S27" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U27" t="n">
-        <v>65.2</v>
+        <v>27.6</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD27" t="inlineStr"/>
@@ -7629,134 +7629,134 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/22, 1 HR</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.5% barrel, 16.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.2% barrel, 21.7 HR allowed</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>7.51</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>37.79</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>88.62</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>98.8173</t>
+          <t>102.3181</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>0.4336</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.1628</t>
+          <t>0.276</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.327</t>
+          <t>0.333</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>41.01</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>32.69</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>13.9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.1752</t>
+          <t>0.364</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>90.94</t>
+          <t>87.79</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>0.4901</t>
+          <t>0.3799</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.1487</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>33.88</t>
+          <t>27.92</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr"/>
       <c r="BH27" t="inlineStr"/>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr"/>
@@ -8043,27 +8043,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>687952</t>
+          <t>695734</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Christian Encarnacion-Strand</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-26T23:45:00Z</t>
+          <t>2026-08-26T22:45:00Z</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8073,17 +8073,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Michael McGreevy</t>
+          <t>Tanner Gordon</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>700241</t>
+          <t>685299</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -8106,26 +8106,26 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>56.6</v>
+        <v>33</v>
       </c>
       <c r="Q29" t="n">
-        <v>53.9</v>
+        <v>62.6</v>
       </c>
       <c r="R29" t="n">
-        <v>22.1</v>
+        <v>28.2</v>
       </c>
       <c r="S29" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T29" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U29" t="n">
-        <v>45.9</v>
+        <v>63.7</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -8201,114 +8201,114 @@
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.6% barrel, 16.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.5% barrel, 16.0 HR allowed</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>14.67</t>
+          <t>7.51</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>37.79</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>90.63</t>
+          <t>88.62</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>101.5339</t>
+          <t>98.8173</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>0.4792</t>
+          <t>0.4336</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.1628</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>0.3133</t>
+          <t>0.327</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>73.81</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>37.81</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>43.08</t>
+          <t>41.01</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>32.69</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>13.9</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>0.1752</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>90.94</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>0.4738</t>
+          <t>0.4901</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>0.1956</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>33.88</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr"/>
       <c r="BH29" t="inlineStr"/>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr"/>
@@ -9147,27 +9147,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>695600</t>
+          <t>687263</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Zach Neto</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-26T23:07:00Z</t>
+          <t>2026-08-26T20:07:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9180,11 +9180,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Joey Cantillo</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>676282</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L33" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9198,26 +9210,26 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>55.2</v>
+        <v>47.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>41.2</v>
+        <v>36.3</v>
       </c>
       <c r="R33" t="n">
-        <v>30.4</v>
+        <v>28.2</v>
       </c>
       <c r="S33" t="n">
         <v>88.7</v>
       </c>
       <c r="T33" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U33" t="n">
-        <v>36</v>
+        <v>81.7</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -9256,7 +9268,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr"/>
@@ -9273,110 +9285,134 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 13.5 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>42.33</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>92.18</t>
+          <t>89.95</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>102.707</t>
+          <t>100.2815</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.4447</t>
+          <t>0.4299</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.209</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.3364</t>
+          <t>0.316</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>71.33</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>13.83</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>34.4</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.2031</t>
-        </is>
-      </c>
-      <c r="BA33" t="inlineStr"/>
-      <c r="BB33" t="inlineStr"/>
-      <c r="BC33" t="inlineStr"/>
-      <c r="BD33" t="inlineStr"/>
-      <c r="BE33" t="inlineStr"/>
-      <c r="BF33" t="inlineStr"/>
+          <t>0.203</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>7.69</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>40.33</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>88.52</t>
+        </is>
+      </c>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>0.3672</t>
+        </is>
+      </c>
+      <c r="BE33" t="inlineStr">
+        <is>
+          <t>0.1375</t>
+        </is>
+      </c>
+      <c r="BF33" t="inlineStr">
+        <is>
+          <t>26.88</t>
+        </is>
+      </c>
       <c r="BG33" t="inlineStr"/>
       <c r="BH33" t="inlineStr"/>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr"/>
@@ -9387,27 +9423,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>687263</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Zach Neto</t>
+          <t>Fernando Tatis</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-26T20:07:00Z</t>
+          <t>2026-08-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9422,17 +9458,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Joey Cantillo</t>
+          <t>Bubba Chandler</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>676282</t>
+          <t>696149</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -9450,26 +9486,26 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>47.8</v>
+        <v>56.9</v>
       </c>
       <c r="Q34" t="n">
-        <v>36.3</v>
+        <v>34.2</v>
       </c>
       <c r="R34" t="n">
-        <v>28.2</v>
+        <v>22.6</v>
       </c>
       <c r="S34" t="n">
         <v>88.7</v>
       </c>
       <c r="T34" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U34" t="n">
-        <v>81.7</v>
+        <v>97</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -9525,134 +9561,134 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 4 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 13.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.7% barrel, 8.3 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>12.32</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>42.33</t>
+          <t>53.55</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>89.95</t>
+          <t>93.09</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>100.2815</t>
+          <t>104.4937</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.4299</t>
+          <t>0.4873</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>0.1981</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.3742</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>71.33</t>
+          <t>75.58</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>13.83</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>35.15</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>34.4</t>
+          <t>22.29</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>19.4</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.203</t>
+          <t>0.1668</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>40.33</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>88.52</t>
+          <t>89.22</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.3672</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1375</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>26.09</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr"/>
       <c r="BH34" t="inlineStr"/>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9663,27 +9699,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>695600</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fernando Tatis</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-26T20:10:00Z</t>
+          <t>2026-08-26T23:07:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9696,21 +9732,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Bubba Chandler</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>696149</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
         <v>52.2</v>
       </c>
@@ -9726,26 +9750,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>56.9</v>
+        <v>55.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>34.2</v>
+        <v>41.2</v>
       </c>
       <c r="R35" t="n">
-        <v>22.6</v>
+        <v>30.4</v>
       </c>
       <c r="S35" t="n">
         <v>88.7</v>
       </c>
       <c r="T35" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U35" t="n">
-        <v>97</v>
+        <v>34.4</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -9784,7 +9808,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr"/>
@@ -9801,134 +9825,110 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Hot streak: 4 HR in last 7 games</t>
+          <t>Last 7 games: 5/22, 1 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.7% barrel, 8.3 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>13.45</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>53.55</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>93.09</t>
+          <t>92.18</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>104.4937</t>
+          <t>102.707</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.4873</t>
+          <t>0.4447</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.1981</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.3742</t>
+          <t>0.3364</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>58.33</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>35.15</t>
+          <t>39.95</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>22.29</t>
+          <t>30.49</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>19.4</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1668</t>
-        </is>
-      </c>
-      <c r="BA35" t="inlineStr">
-        <is>
-          <t>6.74</t>
-        </is>
-      </c>
-      <c r="BB35" t="inlineStr">
-        <is>
-          <t>39.02</t>
-        </is>
-      </c>
-      <c r="BC35" t="inlineStr">
-        <is>
-          <t>89.22</t>
-        </is>
-      </c>
-      <c r="BD35" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="BE35" t="inlineStr">
-        <is>
-          <t>0.149</t>
-        </is>
-      </c>
-      <c r="BF35" t="inlineStr">
-        <is>
-          <t>26.09</t>
-        </is>
-      </c>
+          <t>0.2031</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr"/>
+      <c r="BB35" t="inlineStr"/>
+      <c r="BC35" t="inlineStr"/>
+      <c r="BD35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr"/>
+      <c r="BF35" t="inlineStr"/>
       <c r="BG35" t="inlineStr"/>
       <c r="BH35" t="inlineStr"/>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -12387,27 +12387,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>681715</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Heriberto Hernandez</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-26T23:10:00Z</t>
+          <t>2026-08-26T22:40:00Z</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -12417,17 +12417,17 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Robert Stock</t>
+          <t>Sonny Gray</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>476594</t>
+          <t>543243</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -12436,7 +12436,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -12454,22 +12454,22 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>50.9</v>
+        <v>54.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>50.5</v>
+        <v>37.2</v>
       </c>
       <c r="R45" t="n">
-        <v>24.8</v>
+        <v>21.5</v>
       </c>
       <c r="S45" t="n">
-        <v>88.7</v>
+        <v>95.5</v>
       </c>
       <c r="T45" t="n">
         <v>50</v>
       </c>
       <c r="U45" t="n">
-        <v>28.2</v>
+        <v>60.7</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -12525,134 +12525,134 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.3% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 18.0 HR allowed</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>45.52</t>
+          <t>47.71</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>91.05</t>
+          <t>91.18</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>101.9189</t>
+          <t>101.7587</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>0.4589</t>
+          <t>0.4644</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>0.2042</t>
+          <t>0.2173</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3445</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>74.14</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>45.53</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>28.01</t>
+          <t>29.71</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>16.3</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>0.207</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>10.28</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="BD45" t="inlineStr">
         <is>
-          <t>0.4806</t>
+          <t>0.3845</t>
         </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
-          <t>0.2047</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>36.78</t>
+          <t>22.92</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr"/>
       <c r="BH45" t="inlineStr"/>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr"/>
@@ -12663,27 +12663,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>681715</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Heriberto Hernandez</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-26T22:40:00Z</t>
+          <t>2026-08-26T23:10:00Z</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -12693,17 +12693,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Sonny Gray</t>
+          <t>Robert Stock</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>543243</t>
+          <t>476594</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -12730,22 +12730,22 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>54.2</v>
+        <v>50.9</v>
       </c>
       <c r="Q46" t="n">
-        <v>37.2</v>
+        <v>50.5</v>
       </c>
       <c r="R46" t="n">
-        <v>21.5</v>
+        <v>24.8</v>
       </c>
       <c r="S46" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T46" t="n">
         <v>50</v>
       </c>
       <c r="U46" t="n">
-        <v>60.7</v>
+        <v>26.4</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -12801,134 +12801,134 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 8/27, 0 HR</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 18.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.3% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>47.71</t>
+          <t>45.52</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>91.18</t>
+          <t>91.05</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>101.7587</t>
+          <t>101.9189</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>0.4644</t>
+          <t>0.4589</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>0.2173</t>
+          <t>0.2042</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>0.3445</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>74.14</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>45.53</t>
+          <t>43.61</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>29.71</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>16.3</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>0.186</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>10.28</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>33.97</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>89.19</t>
         </is>
       </c>
       <c r="BD46" t="inlineStr">
         <is>
-          <t>0.3845</t>
+          <t>0.4806</t>
         </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.2047</t>
         </is>
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>22.92</t>
+          <t>36.78</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr"/>
       <c r="BH46" t="inlineStr"/>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr"/>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Last 7 games: 2/18, 1 HR</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
@@ -15745,7 +15745,7 @@
         <v>80</v>
       </c>
       <c r="U57" t="n">
-        <v>27.6</v>
+        <v>26.4</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -15806,7 +15806,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 1 HR</t>
+          <t>Last 7 games: 4/23, 1 HR</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ68" t="inlineStr">
@@ -18816,7 +18816,7 @@
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/26, 0 HR</t>
+          <t>Last 7 games: 3/27, 0 HR</t>
         </is>
       </c>
       <c r="AL68" t="inlineStr">
@@ -22816,7 +22816,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>50</v>
       </c>
       <c r="U83" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -22910,7 +22910,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -22920,7 +22920,7 @@
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 0 HR</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL83" t="inlineStr">
@@ -24217,7 +24217,7 @@
         <v>60</v>
       </c>
       <c r="U88" t="n">
-        <v>46.4</v>
+        <v>45.5</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -26247,27 +26247,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Willi Castro</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-26T23:05:00Z</t>
+          <t>2026-08-26T22:45:00Z</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -26277,26 +26277,14 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Peter Lambert</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>663567</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
       <c r="L96" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -26310,26 +26298,26 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>29.8</v>
+        <v>31.7</v>
       </c>
       <c r="Q96" t="n">
-        <v>33</v>
+        <v>40.2</v>
       </c>
       <c r="R96" t="n">
-        <v>38.2</v>
+        <v>28.2</v>
       </c>
       <c r="S96" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T96" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U96" t="n">
-        <v>50.3</v>
+        <v>62.4</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -26343,7 +26331,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
@@ -26368,7 +26356,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD96" t="inlineStr"/>
@@ -26385,7 +26373,7 @@
       </c>
       <c r="AH96" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI96" t="inlineStr">
@@ -26395,124 +26383,100 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 12.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>7.9</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>39.89</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>88.86</t>
+          <t>87.54</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>98.599</t>
+          <t>100.2352</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>0.4187</t>
+          <t>0.3876</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>0.1505</t>
+          <t>0.1526</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>0.3405</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>69.68</t>
+          <t>72.51</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>26.04</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>42.46</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>31.64</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>0.1737</t>
-        </is>
-      </c>
-      <c r="BA96" t="inlineStr">
-        <is>
-          <t>6.8</t>
-        </is>
-      </c>
-      <c r="BB96" t="inlineStr">
-        <is>
-          <t>36.6</t>
-        </is>
-      </c>
-      <c r="BC96" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
-      </c>
-      <c r="BD96" t="inlineStr">
-        <is>
-          <t>0.347</t>
-        </is>
-      </c>
-      <c r="BE96" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="BF96" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
+          <t>0.1568</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr"/>
+      <c r="BB96" t="inlineStr"/>
+      <c r="BC96" t="inlineStr"/>
+      <c r="BD96" t="inlineStr"/>
+      <c r="BE96" t="inlineStr"/>
+      <c r="BF96" t="inlineStr"/>
       <c r="BG96" t="inlineStr"/>
       <c r="BH96" t="inlineStr"/>
       <c r="BI96" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ96" t="inlineStr"/>
@@ -26523,27 +26487,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>650489</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Willi Castro</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-26T22:45:00Z</t>
+          <t>2026-08-26T23:05:00Z</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -26553,12 +26517,24 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Peter Lambert</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>663567</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L97" t="n">
         <v>45.7</v>
       </c>
@@ -26574,26 +26550,26 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>31.7</v>
+        <v>29.8</v>
       </c>
       <c r="Q97" t="n">
-        <v>40.2</v>
+        <v>33</v>
       </c>
       <c r="R97" t="n">
-        <v>28.2</v>
+        <v>38.2</v>
       </c>
       <c r="S97" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T97" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U97" t="n">
-        <v>62.4</v>
+        <v>48.3</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -26607,7 +26583,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -26632,7 +26608,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr"/>
@@ -26649,110 +26625,134 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>7.9</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>39.89</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>87.54</t>
+          <t>88.86</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>100.2352</t>
+          <t>98.599</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>0.3876</t>
+          <t>0.4187</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>0.1526</t>
+          <t>0.1505</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>0.3081</t>
+          <t>0.3405</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>72.51</t>
+          <t>69.68</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>42.46</t>
+          <t>42.19</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>31.64</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>0.1568</t>
-        </is>
-      </c>
-      <c r="BA97" t="inlineStr"/>
-      <c r="BB97" t="inlineStr"/>
-      <c r="BC97" t="inlineStr"/>
-      <c r="BD97" t="inlineStr"/>
-      <c r="BE97" t="inlineStr"/>
-      <c r="BF97" t="inlineStr"/>
+          <t>0.1737</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>36.6</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>0.347</t>
+        </is>
+      </c>
+      <c r="BE97" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="BF97" t="inlineStr">
+        <is>
+          <t>33.0</t>
+        </is>
+      </c>
       <c r="BG97" t="inlineStr"/>
       <c r="BH97" t="inlineStr"/>
       <c r="BI97" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ97" t="inlineStr"/>
@@ -47067,27 +47067,27 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>664983</t>
+          <t>699393</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Jake McCarthy</t>
+          <t>Pedro Ramirez</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-26T22:45:00Z</t>
+          <t>2026-08-26T19:40:00Z</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -47097,14 +47097,26 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="J173" t="inlineStr"/>
-      <c r="K173" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Eduardo Rodriguez</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>593958</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L173" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -47118,26 +47130,26 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P173" t="n">
-        <v>15</v>
+        <v>22.7</v>
       </c>
       <c r="Q173" t="n">
-        <v>41.2</v>
+        <v>38.4</v>
       </c>
       <c r="R173" t="n">
         <v>28.2</v>
       </c>
       <c r="S173" t="n">
-        <v>88.7</v>
+        <v>59.8</v>
       </c>
       <c r="T173" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U173" t="n">
-        <v>24.9</v>
+        <v>37.8</v>
       </c>
       <c r="V173" t="inlineStr">
         <is>
@@ -47151,7 +47163,7 @@
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y173" t="inlineStr">
@@ -47176,7 +47188,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr"/>
@@ -47193,7 +47205,7 @@
       </c>
       <c r="AH173" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI173" t="inlineStr">
@@ -47203,17 +47215,17 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/28, 0 HR</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AL173" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.1% barrel, 17.3 HR allowed</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
@@ -47223,80 +47235,104 @@
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>84.91</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
         <is>
-          <t>96.7515</t>
+          <t>100.0464</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>0.3964</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>0.1322</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr">
         <is>
-          <t>0.3098</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>70.82</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>37.6</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>0.1739</t>
-        </is>
-      </c>
-      <c r="BA173" t="inlineStr"/>
-      <c r="BB173" t="inlineStr"/>
-      <c r="BC173" t="inlineStr"/>
-      <c r="BD173" t="inlineStr"/>
-      <c r="BE173" t="inlineStr"/>
-      <c r="BF173" t="inlineStr"/>
+          <t>0.149</t>
+        </is>
+      </c>
+      <c r="BA173" t="inlineStr">
+        <is>
+          <t>8.06</t>
+        </is>
+      </c>
+      <c r="BB173" t="inlineStr">
+        <is>
+          <t>34.85</t>
+        </is>
+      </c>
+      <c r="BC173" t="inlineStr">
+        <is>
+          <t>87.85</t>
+        </is>
+      </c>
+      <c r="BD173" t="inlineStr">
+        <is>
+          <t>0.4345</t>
+        </is>
+      </c>
+      <c r="BE173" t="inlineStr">
+        <is>
+          <t>0.172</t>
+        </is>
+      </c>
+      <c r="BF173" t="inlineStr">
+        <is>
+          <t>27.33</t>
+        </is>
+      </c>
       <c r="BG173" t="inlineStr"/>
       <c r="BH173" t="inlineStr"/>
       <c r="BI173" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ173" t="inlineStr"/>
@@ -47307,27 +47343,27 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>699393</t>
+          <t>664983</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Pedro Ramirez</t>
+          <t>Jake McCarthy</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-08-26T19:40:00Z</t>
+          <t>2026-08-26T22:45:00Z</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -47337,24 +47373,12 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>Eduardo Rodriguez</t>
-        </is>
-      </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>593958</t>
-        </is>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
       <c r="L174" t="n">
         <v>38</v>
       </c>
@@ -47370,26 +47394,26 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P174" t="n">
-        <v>22.7</v>
+        <v>15</v>
       </c>
       <c r="Q174" t="n">
-        <v>38.4</v>
+        <v>41.2</v>
       </c>
       <c r="R174" t="n">
         <v>28.2</v>
       </c>
       <c r="S174" t="n">
-        <v>59.8</v>
+        <v>88.7</v>
       </c>
       <c r="T174" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="U174" t="n">
-        <v>37.8</v>
+        <v>23.4</v>
       </c>
       <c r="V174" t="inlineStr">
         <is>
@@ -47403,7 +47427,7 @@
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y174" t="inlineStr">
@@ -47428,7 +47452,7 @@
       </c>
       <c r="AC174" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD174" t="inlineStr"/>
@@ -47445,27 +47469,27 @@
       </c>
       <c r="AH174" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 1 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL174" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.1% barrel, 17.3 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM174" t="inlineStr">
@@ -47475,104 +47499,80 @@
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>84.91</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>100.0464</t>
+          <t>96.7515</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>0.3964</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.1322</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.3098</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>70.82</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>37.6</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>0.149</t>
-        </is>
-      </c>
-      <c r="BA174" t="inlineStr">
-        <is>
-          <t>8.06</t>
-        </is>
-      </c>
-      <c r="BB174" t="inlineStr">
-        <is>
-          <t>34.85</t>
-        </is>
-      </c>
-      <c r="BC174" t="inlineStr">
-        <is>
-          <t>87.85</t>
-        </is>
-      </c>
-      <c r="BD174" t="inlineStr">
-        <is>
-          <t>0.4345</t>
-        </is>
-      </c>
-      <c r="BE174" t="inlineStr">
-        <is>
-          <t>0.172</t>
-        </is>
-      </c>
-      <c r="BF174" t="inlineStr">
-        <is>
-          <t>27.33</t>
-        </is>
-      </c>
+          <t>0.1739</t>
+        </is>
+      </c>
+      <c r="BA174" t="inlineStr"/>
+      <c r="BB174" t="inlineStr"/>
+      <c r="BC174" t="inlineStr"/>
+      <c r="BD174" t="inlineStr"/>
+      <c r="BE174" t="inlineStr"/>
+      <c r="BF174" t="inlineStr"/>
       <c r="BG174" t="inlineStr"/>
       <c r="BH174" t="inlineStr"/>
       <c r="BI174" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ174" t="inlineStr"/>
@@ -60303,27 +60303,27 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>664728</t>
+          <t>701852</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Drew Cavanaugh</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-08-26T23:07:00Z</t>
+          <t>2026-08-26T19:45:00Z</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -60333,14 +60333,26 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I222" t="inlineStr"/>
-      <c r="J222" t="inlineStr"/>
-      <c r="K222" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Nick Lodolo</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>666157</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L222" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="M222" t="inlineStr">
         <is>
@@ -60358,22 +60370,22 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>14.1</v>
+        <v>7</v>
       </c>
       <c r="Q222" t="n">
-        <v>41.2</v>
+        <v>48.7</v>
       </c>
       <c r="R222" t="n">
-        <v>30.4</v>
+        <v>19.3</v>
       </c>
       <c r="S222" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T222" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U222" t="n">
-        <v>64.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V222" t="inlineStr">
         <is>
@@ -60387,7 +60399,7 @@
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y222" t="inlineStr">
@@ -60412,7 +60424,7 @@
       </c>
       <c r="AC222" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD222" t="inlineStr"/>
@@ -60429,27 +60441,27 @@
       </c>
       <c r="AH222" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI222" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL222" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.8% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM222" t="inlineStr">
@@ -60459,80 +60471,104 @@
       </c>
       <c r="AN222" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
         <is>
-          <t>35.26</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>88.64</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AQ222" t="inlineStr">
         <is>
-          <t>99.2362</t>
+          <t>97.8732</t>
         </is>
       </c>
       <c r="AR222" t="inlineStr">
         <is>
-          <t>0.3187</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>0.0861</t>
+          <t>0.098</t>
         </is>
       </c>
       <c r="AT222" t="inlineStr">
         <is>
-          <t>0.2671</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="AU222" t="inlineStr">
         <is>
-          <t>71.17</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>14.25</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>18.66</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>0.1197</t>
-        </is>
-      </c>
-      <c r="BA222" t="inlineStr"/>
-      <c r="BB222" t="inlineStr"/>
-      <c r="BC222" t="inlineStr"/>
-      <c r="BD222" t="inlineStr"/>
-      <c r="BE222" t="inlineStr"/>
-      <c r="BF222" t="inlineStr"/>
+          <t>0.012</t>
+        </is>
+      </c>
+      <c r="BA222" t="inlineStr">
+        <is>
+          <t>8.83</t>
+        </is>
+      </c>
+      <c r="BB222" t="inlineStr">
+        <is>
+          <t>40.08</t>
+        </is>
+      </c>
+      <c r="BC222" t="inlineStr">
+        <is>
+          <t>89.99</t>
+        </is>
+      </c>
+      <c r="BD222" t="inlineStr">
+        <is>
+          <t>0.458</t>
+        </is>
+      </c>
+      <c r="BE222" t="inlineStr">
+        <is>
+          <t>0.1778</t>
+        </is>
+      </c>
+      <c r="BF222" t="inlineStr">
+        <is>
+          <t>25.49</t>
+        </is>
+      </c>
       <c r="BG222" t="inlineStr"/>
       <c r="BH222" t="inlineStr"/>
       <c r="BI222" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ222" t="inlineStr"/>
@@ -60543,27 +60579,27 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>701852</t>
+          <t>664728</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Drew Cavanaugh</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>2026-08-26T19:45:00Z</t>
+          <t>2026-08-26T23:07:00Z</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -60573,24 +60609,12 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>Nick Lodolo</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>666157</t>
-        </is>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr"/>
       <c r="L223" t="n">
         <v>33.3</v>
       </c>
@@ -60610,22 +60634,22 @@
         </is>
       </c>
       <c r="P223" t="n">
-        <v>7</v>
+        <v>14.1</v>
       </c>
       <c r="Q223" t="n">
-        <v>48.7</v>
+        <v>41.2</v>
       </c>
       <c r="R223" t="n">
-        <v>19.3</v>
+        <v>30.4</v>
       </c>
       <c r="S223" t="n">
-        <v>81.90000000000001</v>
+        <v>40.2</v>
       </c>
       <c r="T223" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U223" t="n">
-        <v>9.300000000000001</v>
+        <v>62.4</v>
       </c>
       <c r="V223" t="inlineStr">
         <is>
@@ -60639,7 +60663,7 @@
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y223" t="inlineStr">
@@ -60664,7 +60688,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr"/>
@@ -60681,27 +60705,27 @@
       </c>
       <c r="AH223" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI223" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL223" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.8% barrel, 15.7 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM223" t="inlineStr">
@@ -60711,104 +60735,80 @@
       </c>
       <c r="AN223" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>35.26</t>
         </is>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.64</t>
         </is>
       </c>
       <c r="AQ223" t="inlineStr">
         <is>
-          <t>97.8732</t>
+          <t>99.2362</t>
         </is>
       </c>
       <c r="AR223" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3187</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>0.0861</t>
         </is>
       </c>
       <c r="AT223" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.2671</t>
         </is>
       </c>
       <c r="AU223" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>71.17</t>
         </is>
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>14.25</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>21.9</t>
+          <t>18.66</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>0.012</t>
-        </is>
-      </c>
-      <c r="BA223" t="inlineStr">
-        <is>
-          <t>8.83</t>
-        </is>
-      </c>
-      <c r="BB223" t="inlineStr">
-        <is>
-          <t>40.08</t>
-        </is>
-      </c>
-      <c r="BC223" t="inlineStr">
-        <is>
-          <t>89.99</t>
-        </is>
-      </c>
-      <c r="BD223" t="inlineStr">
-        <is>
-          <t>0.458</t>
-        </is>
-      </c>
-      <c r="BE223" t="inlineStr">
-        <is>
-          <t>0.1778</t>
-        </is>
-      </c>
-      <c r="BF223" t="inlineStr">
-        <is>
-          <t>25.49</t>
-        </is>
-      </c>
+          <t>0.1197</t>
+        </is>
+      </c>
+      <c r="BA223" t="inlineStr"/>
+      <c r="BB223" t="inlineStr"/>
+      <c r="BC223" t="inlineStr"/>
+      <c r="BD223" t="inlineStr"/>
+      <c r="BE223" t="inlineStr"/>
+      <c r="BF223" t="inlineStr"/>
       <c r="BG223" t="inlineStr"/>
       <c r="BH223" t="inlineStr"/>
       <c r="BI223" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ223" t="inlineStr"/>
@@ -61371,27 +61371,27 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>657136</t>
+          <t>702222</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Connor Wong</t>
+          <t>Justin Crawford</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>2026-08-26T22:40:00Z</t>
+          <t>2026-08-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -61401,17 +61401,17 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Ryan Gusto</t>
+          <t>Bryan Woo</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>687473</t>
+          <t>693433</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -61420,7 +61420,7 @@
         </is>
       </c>
       <c r="L226" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="M226" t="inlineStr">
         <is>
@@ -61434,26 +61434,26 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P226" t="n">
-        <v>17.8</v>
+        <v>10.7</v>
       </c>
       <c r="Q226" t="n">
-        <v>48.2</v>
+        <v>42</v>
       </c>
       <c r="R226" t="n">
-        <v>21.5</v>
+        <v>25.4</v>
       </c>
       <c r="S226" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T226" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U226" t="n">
-        <v>39.5</v>
+        <v>26.1</v>
       </c>
       <c r="V226" t="inlineStr">
         <is>
@@ -61467,7 +61467,7 @@
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y226" t="inlineStr">
@@ -61492,7 +61492,7 @@
       </c>
       <c r="AC226" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD226" t="inlineStr"/>
@@ -61509,27 +61509,27 @@
       </c>
       <c r="AH226" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI226" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Last 7 games: 5/17, 0 HR</t>
         </is>
       </c>
       <c r="AL226" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.9% barrel, 10.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 18.3 HR allowed</t>
         </is>
       </c>
       <c r="AM226" t="inlineStr">
@@ -61539,104 +61539,104 @@
       </c>
       <c r="AN226" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>35.2</t>
         </is>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>86.55</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
         <is>
-          <t>99.2106</t>
+          <t>98.142</t>
         </is>
       </c>
       <c r="AR226" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.321</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.063</t>
         </is>
       </c>
       <c r="AT226" t="inlineStr">
         <is>
-          <t>0.2898</t>
+          <t>0.283</t>
         </is>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>72.65</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>27.12</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>40.73</t>
+          <t>26.6</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>23.63</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>0.1089</t>
+          <t>0.088</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>8.87</t>
+          <t>7.56</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>89.59</t>
         </is>
       </c>
       <c r="BD226" t="inlineStr">
         <is>
-          <t>0.4278</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="BE226" t="inlineStr">
         <is>
-          <t>0.1683</t>
+          <t>0.1499</t>
         </is>
       </c>
       <c r="BF226" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>28.69</t>
         </is>
       </c>
       <c r="BG226" t="inlineStr"/>
       <c r="BH226" t="inlineStr"/>
       <c r="BI226" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ226" t="inlineStr"/>
@@ -61647,27 +61647,27 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>702222</t>
+          <t>657136</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Justin Crawford</t>
+          <t>Connor Wong</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>2026-08-26T20:10:00Z</t>
+          <t>2026-08-26T22:40:00Z</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -61677,17 +61677,17 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Bryan Woo</t>
+          <t>Ryan Gusto</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>693433</t>
+          <t>687473</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -61710,26 +61710,26 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P227" t="n">
-        <v>10.7</v>
+        <v>17.8</v>
       </c>
       <c r="Q227" t="n">
-        <v>42</v>
+        <v>48.2</v>
       </c>
       <c r="R227" t="n">
-        <v>25.4</v>
+        <v>21.5</v>
       </c>
       <c r="S227" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T227" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U227" t="n">
-        <v>26.1</v>
+        <v>37.8</v>
       </c>
       <c r="V227" t="inlineStr">
         <is>
@@ -61743,7 +61743,7 @@
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y227" t="inlineStr">
@@ -61768,7 +61768,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr"/>
@@ -61785,27 +61785,27 @@
       </c>
       <c r="AH227" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL227" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 18.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.9% barrel, 10.7 HR allowed</t>
         </is>
       </c>
       <c r="AM227" t="inlineStr">
@@ -61815,104 +61815,104 @@
       </c>
       <c r="AN227" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>35.34</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>86.55</t>
         </is>
       </c>
       <c r="AQ227" t="inlineStr">
         <is>
-          <t>98.142</t>
+          <t>99.2106</t>
         </is>
       </c>
       <c r="AR227" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0.109</t>
         </is>
       </c>
       <c r="AT227" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>0.2898</t>
         </is>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>72.65</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>27.12</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>26.6</t>
+          <t>40.73</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>23.63</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>0.1089</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>7.56</t>
+          <t>8.87</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>89.59</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD227" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.4278</t>
         </is>
       </c>
       <c r="BE227" t="inlineStr">
         <is>
-          <t>0.1499</t>
+          <t>0.1683</t>
         </is>
       </c>
       <c r="BF227" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="BG227" t="inlineStr"/>
       <c r="BH227" t="inlineStr"/>
       <c r="BI227" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ227" t="inlineStr"/>
@@ -62751,24 +62751,24 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>691011</t>
+          <t>643376</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Drew Romo</t>
+          <t>Danny Jansen</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
+          <t>TEX</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>TEX</t>
-        </is>
-      </c>
       <c r="F231" t="inlineStr">
         <is>
           <t>2026-08-26T23:40:00Z</t>
@@ -62786,17 +62786,17 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>669022</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L231" t="n">
@@ -62814,14 +62814,14 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P231" t="n">
-        <v>9.9</v>
+        <v>19.6</v>
       </c>
       <c r="Q231" t="n">
-        <v>44.9</v>
+        <v>44.4</v>
       </c>
       <c r="R231" t="n">
         <v>27.6</v>
@@ -62830,10 +62830,10 @@
         <v>40.2</v>
       </c>
       <c r="T231" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U231" t="n">
-        <v>33.7</v>
+        <v>18.3</v>
       </c>
       <c r="V231" t="inlineStr">
         <is>
@@ -62889,12 +62889,12 @@
       </c>
       <c r="AH231" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ231" t="inlineStr">
@@ -62904,112 +62904,112 @@
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 1 HR</t>
+          <t>Last 7 games: 1/14, 1 HR</t>
         </is>
       </c>
       <c r="AL231" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.5% barrel, 18.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.4% barrel, 18.8 HR allowed</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN231" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>33.75</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>87.11</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>95.305</t>
+          <t>97.4711</t>
         </is>
       </c>
       <c r="AR231" t="inlineStr">
         <is>
-          <t>0.2086</t>
+          <t>0.2888</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>0.0777</t>
+          <t>0.1164</t>
         </is>
       </c>
       <c r="AT231" t="inlineStr">
         <is>
-          <t>0.1785</t>
+          <t>0.2598</t>
         </is>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>68.49</t>
+          <t>70.06</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>7.02</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>54.75</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>28.56</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>0.1455</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>42.56</t>
+          <t>39.06</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.32</t>
         </is>
       </c>
       <c r="BD231" t="inlineStr">
         <is>
-          <t>0.3877</t>
+          <t>0.3968</t>
         </is>
       </c>
       <c r="BE231" t="inlineStr">
         <is>
-          <t>0.1516</t>
+          <t>0.1634</t>
         </is>
       </c>
       <c r="BF231" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>30.98</t>
         </is>
       </c>
       <c r="BG231" t="inlineStr"/>
@@ -63027,27 +63027,27 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>691011</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Drew Romo</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-08-26T17:10:00Z</t>
+          <t>2026-08-26T23:40:00Z</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -63057,26 +63057,26 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Troy Melton</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>675512</t>
+          <t>669022</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L232" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="M232" t="inlineStr">
         <is>
@@ -63090,26 +63090,26 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P232" t="n">
-        <v>12</v>
+        <v>9.9</v>
       </c>
       <c r="Q232" t="n">
-        <v>33.1</v>
+        <v>44.9</v>
       </c>
       <c r="R232" t="n">
         <v>27.6</v>
       </c>
       <c r="S232" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T232" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U232" t="n">
-        <v>32</v>
+        <v>33.7</v>
       </c>
       <c r="V232" t="inlineStr">
         <is>
@@ -63123,7 +63123,7 @@
       </c>
       <c r="X232" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y232" t="inlineStr">
@@ -63165,27 +63165,27 @@
       </c>
       <c r="AH232" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI232" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 4/18, 1 HR</t>
         </is>
       </c>
       <c r="AL232" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 9.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.5% barrel, 18.6 HR allowed</t>
         </is>
       </c>
       <c r="AM232" t="inlineStr">
@@ -63195,104 +63195,104 @@
       </c>
       <c r="AN232" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>85.53</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="AQ232" t="inlineStr">
         <is>
-          <t>97.4095</t>
+          <t>95.305</t>
         </is>
       </c>
       <c r="AR232" t="inlineStr">
         <is>
-          <t>0.3493</t>
+          <t>0.2086</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr">
         <is>
-          <t>0.0998</t>
+          <t>0.0777</t>
         </is>
       </c>
       <c r="AT232" t="inlineStr">
         <is>
-          <t>0.2754</t>
+          <t>0.1785</t>
         </is>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>72.82</t>
+          <t>68.49</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>29.78</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>21.71</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>0.1538</t>
+          <t>0.112</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>6.78</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>42.56</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>89.05</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="BD232" t="inlineStr">
         <is>
-          <t>0.3612</t>
+          <t>0.3877</t>
         </is>
       </c>
       <c r="BE232" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.1516</t>
         </is>
       </c>
       <c r="BF232" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="BG232" t="inlineStr"/>
       <c r="BH232" t="inlineStr"/>
       <c r="BI232" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ232" t="inlineStr"/>
@@ -63303,24 +63303,24 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>703601</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Max Clark</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
           <t>DET</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F233" t="inlineStr">
         <is>
           <t>2026-08-26T17:10:00Z</t>
@@ -63333,17 +63333,17 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Troy Melton</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>675512</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
@@ -63352,7 +63352,7 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="M233" t="inlineStr">
         <is>
@@ -63366,26 +63366,26 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P233" t="n">
-        <v>15.7</v>
+        <v>12</v>
       </c>
       <c r="Q233" t="n">
-        <v>35.8</v>
+        <v>33.1</v>
       </c>
       <c r="R233" t="n">
         <v>27.6</v>
       </c>
       <c r="S233" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T233" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U233" t="n">
-        <v>27.6</v>
+        <v>32</v>
       </c>
       <c r="V233" t="inlineStr">
         <is>
@@ -63399,7 +63399,7 @@
       </c>
       <c r="X233" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y233" t="inlineStr">
@@ -63424,7 +63424,7 @@
       </c>
       <c r="AC233" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD233" t="inlineStr"/>
@@ -63441,27 +63441,27 @@
       </c>
       <c r="AH233" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI233" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 1 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL233" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 21.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 9.1 HR allowed</t>
         </is>
       </c>
       <c r="AM233" t="inlineStr">
@@ -63471,97 +63471,97 @@
       </c>
       <c r="AN233" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.53</t>
         </is>
       </c>
       <c r="AQ233" t="inlineStr">
         <is>
-          <t>97.3958</t>
+          <t>97.4095</t>
         </is>
       </c>
       <c r="AR233" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.3493</t>
         </is>
       </c>
       <c r="AS233" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.0998</t>
         </is>
       </c>
       <c r="AT233" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0.2754</t>
         </is>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.82</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>29.78</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>46.09</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>21.71</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.1538</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>87.79</t>
+          <t>89.05</t>
         </is>
       </c>
       <c r="BD233" t="inlineStr">
         <is>
-          <t>0.3799</t>
+          <t>0.3612</t>
         </is>
       </c>
       <c r="BE233" t="inlineStr">
         <is>
-          <t>0.1487</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BF233" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="BG233" t="inlineStr"/>
@@ -63579,27 +63579,27 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>663968</t>
+          <t>703601</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Jake Mangum</t>
+          <t>Max Clark</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>2026-08-26T20:10:00Z</t>
+          <t>2026-08-26T17:10:00Z</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -63609,12 +63609,24 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I234" t="inlineStr"/>
-      <c r="J234" t="inlineStr"/>
-      <c r="K234" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Freddy Peralta</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>642547</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L234" t="n">
         <v>32.1</v>
       </c>
@@ -63634,22 +63646,22 @@
         </is>
       </c>
       <c r="P234" t="n">
-        <v>6.3</v>
+        <v>15.7</v>
       </c>
       <c r="Q234" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="R234" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="S234" t="n">
         <v>40.2</v>
       </c>
-      <c r="R234" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="S234" t="n">
-        <v>71.7</v>
-      </c>
       <c r="T234" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U234" t="n">
-        <v>4.5</v>
+        <v>27.6</v>
       </c>
       <c r="V234" t="inlineStr">
         <is>
@@ -63663,7 +63675,7 @@
       </c>
       <c r="X234" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y234" t="inlineStr">
@@ -63688,7 +63700,7 @@
       </c>
       <c r="AC234" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD234" t="inlineStr"/>
@@ -63705,27 +63717,27 @@
       </c>
       <c r="AH234" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI234" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 4/22, 1 HR</t>
         </is>
       </c>
       <c r="AL234" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 21.7 HR allowed</t>
         </is>
       </c>
       <c r="AM234" t="inlineStr">
@@ -63735,80 +63747,104 @@
       </c>
       <c r="AN234" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AQ234" t="inlineStr">
         <is>
-          <t>96.7083</t>
+          <t>97.3958</t>
         </is>
       </c>
       <c r="AR234" t="inlineStr">
         <is>
-          <t>0.3325</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr">
         <is>
-          <t>0.0822</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="AT234" t="inlineStr">
         <is>
-          <t>0.283</t>
+          <t>0.307</t>
         </is>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>67.58</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>27.51</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>0.0846</t>
-        </is>
-      </c>
-      <c r="BA234" t="inlineStr"/>
-      <c r="BB234" t="inlineStr"/>
-      <c r="BC234" t="inlineStr"/>
-      <c r="BD234" t="inlineStr"/>
-      <c r="BE234" t="inlineStr"/>
-      <c r="BF234" t="inlineStr"/>
+          <t>0.122</t>
+        </is>
+      </c>
+      <c r="BA234" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="BB234" t="inlineStr">
+        <is>
+          <t>37.44</t>
+        </is>
+      </c>
+      <c r="BC234" t="inlineStr">
+        <is>
+          <t>87.79</t>
+        </is>
+      </c>
+      <c r="BD234" t="inlineStr">
+        <is>
+          <t>0.3799</t>
+        </is>
+      </c>
+      <c r="BE234" t="inlineStr">
+        <is>
+          <t>0.1487</t>
+        </is>
+      </c>
+      <c r="BF234" t="inlineStr">
+        <is>
+          <t>27.92</t>
+        </is>
+      </c>
       <c r="BG234" t="inlineStr"/>
       <c r="BH234" t="inlineStr"/>
       <c r="BI234" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ234" t="inlineStr"/>
@@ -63819,27 +63855,27 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>663968</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Jake Mangum</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>2026-08-26T17:10:00Z</t>
+          <t>2026-08-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -63849,26 +63885,14 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>Troy Melton</t>
-        </is>
-      </c>
-      <c r="J235" t="inlineStr">
-        <is>
-          <t>675512</t>
-        </is>
-      </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr"/>
       <c r="L235" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="M235" t="inlineStr">
         <is>
@@ -63886,22 +63910,22 @@
         </is>
       </c>
       <c r="P235" t="n">
-        <v>0.2</v>
+        <v>6.3</v>
       </c>
       <c r="Q235" t="n">
-        <v>33.1</v>
+        <v>40.2</v>
       </c>
       <c r="R235" t="n">
-        <v>27.6</v>
+        <v>22.6</v>
       </c>
       <c r="S235" t="n">
-        <v>81.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T235" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U235" t="n">
-        <v>22.4</v>
+        <v>4.5</v>
       </c>
       <c r="V235" t="inlineStr">
         <is>
@@ -63915,7 +63939,7 @@
       </c>
       <c r="X235" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y235" t="inlineStr">
@@ -63940,7 +63964,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD235" t="inlineStr"/>
@@ -63957,12 +63981,12 @@
       </c>
       <c r="AH235" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI235" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ235" t="inlineStr">
@@ -63972,12 +63996,12 @@
       </c>
       <c r="AK235" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 3/20, 0 HR</t>
         </is>
       </c>
       <c r="AL235" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 9.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM235" t="inlineStr">
@@ -63987,104 +64011,80 @@
       </c>
       <c r="AN235" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>84.02</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="AQ235" t="inlineStr">
         <is>
-          <t>92.869</t>
+          <t>96.7083</t>
         </is>
       </c>
       <c r="AR235" t="inlineStr">
         <is>
-          <t>0.3066</t>
+          <t>0.3325</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0822</t>
         </is>
       </c>
       <c r="AT235" t="inlineStr">
         <is>
-          <t>0.2725</t>
+          <t>0.283</t>
         </is>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>64.66</t>
+          <t>67.58</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>4.01</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>28.34</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>12.79</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>0.0528</t>
-        </is>
-      </c>
-      <c r="BA235" t="inlineStr">
-        <is>
-          <t>6.78</t>
-        </is>
-      </c>
-      <c r="BB235" t="inlineStr">
-        <is>
-          <t>39.75</t>
-        </is>
-      </c>
-      <c r="BC235" t="inlineStr">
-        <is>
-          <t>89.05</t>
-        </is>
-      </c>
-      <c r="BD235" t="inlineStr">
-        <is>
-          <t>0.3612</t>
-        </is>
-      </c>
-      <c r="BE235" t="inlineStr">
-        <is>
-          <t>0.1442</t>
-        </is>
-      </c>
-      <c r="BF235" t="inlineStr">
-        <is>
-          <t>25.26</t>
-        </is>
-      </c>
+          <t>0.0846</t>
+        </is>
+      </c>
+      <c r="BA235" t="inlineStr"/>
+      <c r="BB235" t="inlineStr"/>
+      <c r="BC235" t="inlineStr"/>
+      <c r="BD235" t="inlineStr"/>
+      <c r="BE235" t="inlineStr"/>
+      <c r="BF235" t="inlineStr"/>
       <c r="BG235" t="inlineStr"/>
       <c r="BH235" t="inlineStr"/>
       <c r="BI235" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ235" t="inlineStr"/>
@@ -64095,27 +64095,27 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>683766</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Christian Koss</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>2026-08-26T19:45:00Z</t>
+          <t>2026-08-26T17:10:00Z</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -64125,22 +64125,22 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>Nick Lodolo</t>
+          <t>Troy Melton</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>666157</t>
+          <t>675512</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L236" t="n">
@@ -64162,22 +64162,22 @@
         </is>
       </c>
       <c r="P236" t="n">
-        <v>10.8</v>
+        <v>0.2</v>
       </c>
       <c r="Q236" t="n">
-        <v>48.7</v>
+        <v>33.1</v>
       </c>
       <c r="R236" t="n">
-        <v>19.3</v>
+        <v>27.6</v>
       </c>
       <c r="S236" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T236" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U236" t="n">
-        <v>22.9</v>
+        <v>22.4</v>
       </c>
       <c r="V236" t="inlineStr">
         <is>
@@ -64191,7 +64191,7 @@
       </c>
       <c r="X236" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y236" t="inlineStr">
@@ -64233,12 +64233,12 @@
       </c>
       <c r="AH236" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI236" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ236" t="inlineStr">
@@ -64248,12 +64248,12 @@
       </c>
       <c r="AK236" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL236" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.8% barrel, 15.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 9.1 HR allowed</t>
         </is>
       </c>
       <c r="AM236" t="inlineStr">
@@ -64263,104 +64263,104 @@
       </c>
       <c r="AN236" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>85.36</t>
+          <t>84.02</t>
         </is>
       </c>
       <c r="AQ236" t="inlineStr">
         <is>
-          <t>97.2632</t>
+          <t>92.869</t>
         </is>
       </c>
       <c r="AR236" t="inlineStr">
         <is>
-          <t>0.3131</t>
+          <t>0.3066</t>
         </is>
       </c>
       <c r="AS236" t="inlineStr">
         <is>
-          <t>0.0921</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT236" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>0.2725</t>
         </is>
       </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>69.79</t>
+          <t>64.66</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>38.65</t>
+          <t>28.34</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>12.79</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>0.0648</t>
+          <t>0.0528</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>6.78</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>40.08</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>89.99</t>
+          <t>89.05</t>
         </is>
       </c>
       <c r="BD236" t="inlineStr">
         <is>
-          <t>0.458</t>
+          <t>0.3612</t>
         </is>
       </c>
       <c r="BE236" t="inlineStr">
         <is>
-          <t>0.1778</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BF236" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>25.26</t>
         </is>
       </c>
       <c r="BG236" t="inlineStr"/>
       <c r="BH236" t="inlineStr"/>
       <c r="BI236" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ236" t="inlineStr"/>
@@ -64371,27 +64371,27 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>668952</t>
+          <t>683766</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Ryan Kreidler</t>
+          <t>Christian Koss</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>2026-08-27T01:05:00Z</t>
+          <t>2026-08-26T19:45:00Z</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -64406,21 +64406,21 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>J.T. Ginn</t>
+          <t>Nick Lodolo</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>669372</t>
+          <t>666157</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L237" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
@@ -64434,26 +64434,26 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P237" t="n">
-        <v>25.1</v>
+        <v>10.8</v>
       </c>
       <c r="Q237" t="n">
-        <v>30.2</v>
+        <v>48.7</v>
       </c>
       <c r="R237" t="n">
-        <v>30.9</v>
+        <v>19.3</v>
       </c>
       <c r="S237" t="n">
         <v>40.2</v>
       </c>
       <c r="T237" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U237" t="n">
-        <v>30.3</v>
+        <v>22.9</v>
       </c>
       <c r="V237" t="inlineStr">
         <is>
@@ -64509,27 +64509,27 @@
       </c>
       <c r="AH237" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI237" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/5, 1 HR</t>
+          <t>Last 7 games: 6/22, 0 HR</t>
         </is>
       </c>
       <c r="AL237" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.7% barrel, 14.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.8% barrel, 15.7 HR allowed</t>
         </is>
       </c>
       <c r="AM237" t="inlineStr">
@@ -64539,104 +64539,104 @@
       </c>
       <c r="AN237" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>5.58</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>88.34</t>
+          <t>85.36</t>
         </is>
       </c>
       <c r="AQ237" t="inlineStr">
         <is>
-          <t>99.1871</t>
+          <t>97.2632</t>
         </is>
       </c>
       <c r="AR237" t="inlineStr">
         <is>
-          <t>0.3376</t>
+          <t>0.3131</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr">
         <is>
-          <t>0.1301</t>
+          <t>0.0921</t>
         </is>
       </c>
       <c r="AT237" t="inlineStr">
         <is>
-          <t>0.2682</t>
+          <t>0.255</t>
         </is>
       </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>69.79</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>32.16</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>28.58</t>
+          <t>19.82</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>0.1085</t>
+          <t>0.0648</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>40.08</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>89.99</t>
         </is>
       </c>
       <c r="BD237" t="inlineStr">
         <is>
-          <t>0.3663</t>
+          <t>0.458</t>
         </is>
       </c>
       <c r="BE237" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.1778</t>
         </is>
       </c>
       <c r="BF237" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>25.49</t>
         </is>
       </c>
       <c r="BG237" t="inlineStr"/>
       <c r="BH237" t="inlineStr"/>
       <c r="BI237" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ237" t="inlineStr"/>
@@ -64647,27 +64647,27 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>665926</t>
+          <t>668952</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Andres Gimenez</t>
+          <t>Ryan Kreidler</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2026-08-26T23:07:00Z</t>
+          <t>2026-08-27T01:05:00Z</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -64677,17 +64677,17 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Randy Dobnak</t>
+          <t>J.T. Ginn</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>677976</t>
+          <t>669372</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -64696,7 +64696,7 @@
         </is>
       </c>
       <c r="L238" t="n">
-        <v>31.4</v>
+        <v>31.8</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
@@ -64710,26 +64710,26 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P238" t="n">
-        <v>6.5</v>
+        <v>25.1</v>
       </c>
       <c r="Q238" t="n">
-        <v>31.7</v>
+        <v>30.2</v>
       </c>
       <c r="R238" t="n">
-        <v>30.4</v>
+        <v>30.9</v>
       </c>
       <c r="S238" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T238" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U238" t="n">
-        <v>30</v>
+        <v>30.3</v>
       </c>
       <c r="V238" t="inlineStr">
         <is>
@@ -64743,7 +64743,7 @@
       </c>
       <c r="X238" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y238" t="inlineStr">
@@ -64785,27 +64785,27 @@
       </c>
       <c r="AH238" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 1/5, 1 HR</t>
         </is>
       </c>
       <c r="AL238" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.3% barrel, 1.7 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.7% barrel, 14.9 HR allowed</t>
         </is>
       </c>
       <c r="AM238" t="inlineStr">
@@ -64815,104 +64815,104 @@
       </c>
       <c r="AN238" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>6.69</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>88.34</t>
         </is>
       </c>
       <c r="AQ238" t="inlineStr">
         <is>
-          <t>95.7821</t>
+          <t>99.1871</t>
         </is>
       </c>
       <c r="AR238" t="inlineStr">
         <is>
-          <t>0.3316</t>
+          <t>0.3376</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>0.1301</t>
         </is>
       </c>
       <c r="AT238" t="inlineStr">
         <is>
-          <t>0.2786</t>
+          <t>0.2682</t>
         </is>
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>68.46</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>5.14</t>
+          <t>32.16</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>38.45</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>28.58</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>0.1121</t>
+          <t>0.1085</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>37.92</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>91.46</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="BD238" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.3663</t>
         </is>
       </c>
       <c r="BE238" t="inlineStr">
         <is>
-          <t>0.1254</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BF238" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="BG238" t="inlineStr"/>
       <c r="BH238" t="inlineStr"/>
       <c r="BI238" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ238" t="inlineStr"/>
@@ -64923,27 +64923,27 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>643376</t>
+          <t>665926</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Danny Jansen</t>
+          <t>Andres Gimenez</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>2026-08-26T23:40:00Z</t>
+          <t>2026-08-26T23:07:00Z</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -64953,17 +64953,17 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Randy Dobnak</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>677976</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -64986,26 +64986,26 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P239" t="n">
-        <v>19.6</v>
+        <v>6.5</v>
       </c>
       <c r="Q239" t="n">
-        <v>44.4</v>
+        <v>31.7</v>
       </c>
       <c r="R239" t="n">
-        <v>27.6</v>
+        <v>30.4</v>
       </c>
       <c r="S239" t="n">
-        <v>40.2</v>
+        <v>59.8</v>
       </c>
       <c r="T239" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U239" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V239" t="inlineStr">
         <is>
@@ -65019,7 +65019,7 @@
       </c>
       <c r="X239" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y239" t="inlineStr">
@@ -65061,134 +65061,134 @@
       </c>
       <c r="AH239" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI239" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AJ239" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AI239" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AJ239" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK239" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/13, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL239" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.4% barrel, 18.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.3% barrel, 1.7 HR allowed</t>
         </is>
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN239" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>24.55</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>87.11</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ239" t="inlineStr">
         <is>
-          <t>97.4711</t>
+          <t>95.7821</t>
         </is>
       </c>
       <c r="AR239" t="inlineStr">
         <is>
-          <t>0.2888</t>
+          <t>0.3316</t>
         </is>
       </c>
       <c r="AS239" t="inlineStr">
         <is>
-          <t>0.1164</t>
+          <t>0.095</t>
         </is>
       </c>
       <c r="AT239" t="inlineStr">
         <is>
-          <t>0.2598</t>
+          <t>0.2786</t>
         </is>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>70.06</t>
+          <t>68.46</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>7.02</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>54.75</t>
+          <t>38.45</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>28.56</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>0.1455</t>
+          <t>0.1121</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>39.06</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>89.32</t>
+          <t>91.46</t>
         </is>
       </c>
       <c r="BD239" t="inlineStr">
         <is>
-          <t>0.3968</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="BE239" t="inlineStr">
         <is>
-          <t>0.1634</t>
+          <t>0.1254</t>
         </is>
       </c>
       <c r="BF239" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="BG239" t="inlineStr"/>
       <c r="BH239" t="inlineStr"/>
       <c r="BI239" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ239" t="inlineStr"/>
@@ -69998,7 +69998,7 @@
       </c>
       <c r="AI257" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ257" t="inlineStr">
@@ -70008,7 +70008,7 @@
       </c>
       <c r="AK257" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/16, 0 HR</t>
+          <t>Last 7 games: 0/17, 0 HR</t>
         </is>
       </c>
       <c r="AL257" t="inlineStr">
@@ -73564,7 +73564,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -73574,7 +73574,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Contact streak: 11/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -74801,27 +74801,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>700250</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Ben Rice</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-26T20:07:00Z</t>
+          <t>2026-08-26T23:05:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -74831,17 +74831,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -74850,7 +74850,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>57.1</v>
+        <v>57.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -74864,26 +74864,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>55.6</v>
+        <v>64.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>56.9</v>
+        <v>33</v>
       </c>
       <c r="R13" t="n">
-        <v>28.2</v>
+        <v>38.2</v>
       </c>
       <c r="S13" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>74.2</v>
+        <v>36.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -74897,7 +74897,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -74939,134 +74939,134 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.9% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>14.98</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>46.99</t>
+          <t>50.85</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>90.86</t>
+          <t>92.53</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>103.18</t>
+          <t>102.5716</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4853</t>
+          <t>0.5173</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.2246</t>
+          <t>0.2513</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3426</t>
+          <t>0.3756</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>77.32</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>71.41</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38.28</t>
+          <t>46.29</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>27.91</t>
+          <t>30.32</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1937</t>
+          <t>0.2664</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -75077,27 +75077,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>665833</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Oneil Cruz</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-26T20:10:00Z</t>
+          <t>2026-08-26T20:07:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -75107,12 +75107,24 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Grayson Rodriguez</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>680570</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
         <v>57.1</v>
       </c>
@@ -75128,26 +75140,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>74.3</v>
+        <v>55.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>56.9</v>
       </c>
       <c r="R14" t="n">
-        <v>22.6</v>
+        <v>28.2</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>48.7</v>
+        <v>74.2</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -75161,7 +75173,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -75186,7 +75198,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -75203,12 +75215,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -75223,90 +75235,114 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.9% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>17.65</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>57.58</t>
+          <t>46.99</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>95.73</t>
+          <t>90.86</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>107.1754</t>
+          <t>103.18</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4726</t>
+          <t>0.4853</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.2315</t>
+          <t>0.2246</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3471</t>
+          <t>0.3426</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>78.38</t>
+          <t>77.32</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>76.24</t>
+          <t>71.41</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>38.28</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>27.91</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>17.2</t>
+          <t>25.1</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.2088</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+          <t>0.1937</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>9.9</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>46.5</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>90.7</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.477</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>26.2</t>
+        </is>
+      </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -75317,27 +75353,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>700250</t>
+          <t>665833</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ben Rice</t>
+          <t>Oneil Cruz</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-26T23:05:00Z</t>
+          <t>2026-08-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -75347,26 +75383,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Peter Lambert</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>663567</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>57</v>
+        <v>57.1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -75380,26 +75404,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>64.3</v>
+        <v>74.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>33</v>
+        <v>41.2</v>
       </c>
       <c r="R15" t="n">
-        <v>38.2</v>
+        <v>22.6</v>
       </c>
       <c r="S15" t="n">
-        <v>95.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U15" t="n">
-        <v>31.6</v>
+        <v>48.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -75413,7 +75437,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -75438,7 +75462,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -75455,134 +75479,110 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 12.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>14.98</t>
+          <t>17.65</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>50.85</t>
+          <t>57.58</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>92.53</t>
+          <t>95.73</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>102.5716</t>
+          <t>107.1754</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.5173</t>
+          <t>0.4726</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.2513</t>
+          <t>0.2315</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3756</t>
+          <t>0.3471</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>78.38</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>76.24</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>46.29</t>
+          <t>40.23</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>30.32</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>17.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.2664</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>6.8</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>36.6</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>0.347</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
+          <t>0.2088</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -76194,7 +76194,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>54.7</v>
+        <v>54.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -76227,7 +76227,7 @@
         <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>89.2</v>
+        <v>93.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -76283,12 +76283,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
